--- a/assets/excel/2026_1-1-1.xlsx
+++ b/assets/excel/2026_1-1-1.xlsx
@@ -2,19 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="166925"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Hannover\Dez15_Uebergreifende_Analysen\Projekte\Integrationsmonitoring\Schlesier\MT_Site\assets\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BiesterChristophLSN\Desktop\MZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74EE4D1A-E4B7-44B1-A142-40B08BAD5F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4687E1B7-70EA-47D6-A9E2-4E891ADB789C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{10A5E901-1E3B-4FD8-A95C-5E70FBB58270}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{1C896882-FD2C-4B93-9A68-8CC92E541D34}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -27,6 +30,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -37,7 +42,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t>Migration und Teilhabe in Niedersachsen - Integrationsmonitoring 2026</t>
+  </si>
+  <si>
+    <t>Tabelle 1.1.1: Bevölkerung bis 2025</t>
+  </si>
   <si>
     <t>Kreisfreie Stadt
 Landkreis
@@ -62,6 +73,15 @@
     <t>Veränderung</t>
   </si>
   <si>
+    <t>2025 / 2005</t>
+  </si>
+  <si>
+    <t>2025 / 2020</t>
+  </si>
+  <si>
+    <t>2025 / 2024</t>
+  </si>
+  <si>
     <t>Anzahl</t>
   </si>
   <si>
@@ -74,193 +94,13 @@
     <t>Niedersächsisches Ministerium für Soziales, Gesundheit und Gleichstellung (Hrsg.),</t>
   </si>
   <si>
+    <t>© Landesamt für Statistik Niedersachsen, Hannover 2026,                                                                          </t>
+  </si>
+  <si>
     <t>Vervielfältigung und Verbreitung, auch auszugsweise, mit Quellenangabe gestattet.</t>
   </si>
   <si>
     <t>https://www.integrationsmonitoring.niedersachsen.de</t>
-  </si>
-  <si>
-    <t>© Landesamt für Statistik Niedersachsen, Hannover 2026,                                                                          </t>
-  </si>
-  <si>
-    <t>Migration und Teilhabe in Niedersachsen - Integrationsmonitoring 2026</t>
-  </si>
-  <si>
-    <t>Tabelle 1.1.1: Bevölkerung bis 2025</t>
-  </si>
-  <si>
-    <t>2025 / 2005</t>
-  </si>
-  <si>
-    <t>2025 / 2020</t>
-  </si>
-  <si>
-    <t>2025 / 2024</t>
-  </si>
-  <si>
-    <t>Indikator 1.1.1: Bevölkerung in Niedersachsen</t>
-  </si>
-  <si>
-    <t>Braunschweig, Stadt</t>
-  </si>
-  <si>
-    <t>Salzgitter, Stadt</t>
-  </si>
-  <si>
-    <t>Wolfsburg, Stadt</t>
-  </si>
-  <si>
-    <t>Gifhorn</t>
-  </si>
-  <si>
-    <t>Goslar</t>
-  </si>
-  <si>
-    <t>Helmstedt</t>
-  </si>
-  <si>
-    <t>Northeim</t>
-  </si>
-  <si>
-    <t>Peine</t>
-  </si>
-  <si>
-    <t>Wolfenbüttel</t>
-  </si>
-  <si>
-    <t>Göttingen</t>
-  </si>
-  <si>
-    <t>Statistische Region Braunschweig</t>
-  </si>
-  <si>
-    <t>Region Hannover</t>
-  </si>
-  <si>
-    <t>dav. Hannover, Lhst.</t>
-  </si>
-  <si>
-    <t>dav. Hannover, Umland</t>
-  </si>
-  <si>
-    <t>Diepholz</t>
-  </si>
-  <si>
-    <t>Hameln-Pyrmont</t>
-  </si>
-  <si>
-    <t>Hildesheim</t>
-  </si>
-  <si>
-    <t>Holzminden</t>
-  </si>
-  <si>
-    <t>Nienburg (Weser)</t>
-  </si>
-  <si>
-    <t>Schaumburg</t>
-  </si>
-  <si>
-    <t>Statistische Region Hannover</t>
-  </si>
-  <si>
-    <t>Celle</t>
-  </si>
-  <si>
-    <t>Cuxhaven</t>
-  </si>
-  <si>
-    <t>Harburg</t>
-  </si>
-  <si>
-    <t>Lüchow-Dannenberg</t>
-  </si>
-  <si>
-    <t>Lüneburg</t>
-  </si>
-  <si>
-    <t>Osterholz</t>
-  </si>
-  <si>
-    <t>Rotenburg (Wümme)</t>
-  </si>
-  <si>
-    <t>Heidekreis</t>
-  </si>
-  <si>
-    <t>Stade</t>
-  </si>
-  <si>
-    <t>Uelzen</t>
-  </si>
-  <si>
-    <t>Verden</t>
-  </si>
-  <si>
-    <t>Statistische Region Lüneburg</t>
-  </si>
-  <si>
-    <t>Delmenhorst, Stadt</t>
-  </si>
-  <si>
-    <t>Emden, Stadt</t>
-  </si>
-  <si>
-    <t>Oldenburg (Oldb), Stadt</t>
-  </si>
-  <si>
-    <t>Osnabrück, Stadt</t>
-  </si>
-  <si>
-    <t>Wilhelmshaven, Stadt</t>
-  </si>
-  <si>
-    <t>Ammerland</t>
-  </si>
-  <si>
-    <t>Aurich</t>
-  </si>
-  <si>
-    <t>Cloppenburg</t>
-  </si>
-  <si>
-    <t>Emsland</t>
-  </si>
-  <si>
-    <t>Friesland</t>
-  </si>
-  <si>
-    <t>Grafschaft Bentheim</t>
-  </si>
-  <si>
-    <t>Leer</t>
-  </si>
-  <si>
-    <t>Oldenburg</t>
-  </si>
-  <si>
-    <t>Osnabrück</t>
-  </si>
-  <si>
-    <t>Vechta</t>
-  </si>
-  <si>
-    <t>Wesermarsch</t>
-  </si>
-  <si>
-    <t>Wittmund</t>
-  </si>
-  <si>
-    <t>Statistische Region Weser-Ems</t>
-  </si>
-  <si>
-    <t>Niedersachsen</t>
-  </si>
-  <si>
-    <t>Quelle: Bevölkerungsfortschreibung</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -275,14 +115,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -290,7 +130,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -346,7 +186,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -437,15 +277,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -453,17 +284,53 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -475,17 +342,11 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -497,36 +358,24 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
-    <cellStyle name="Standard 2" xfId="2" xr:uid="{AA26A82F-8DBB-48AA-9E3C-F8451ED11FD4}"/>
-    <cellStyle name="Standard_Tabelle_A_6_HT" xfId="3" xr:uid="{5F8A70A1-C2C9-474B-AC06-185FF1609DC8}"/>
+    <cellStyle name="Standard 2" xfId="2" xr:uid="{CA601CF2-F67A-4624-9B60-472D1C88954C}"/>
+    <cellStyle name="Standard_Tabelle_A_6_HT" xfId="3" xr:uid="{F8F214AC-DBCD-40A0-9E65-D08D80A15EC8}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -541,10 +390,378 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="1_1_1_Download"/>
+      <sheetName val="A1_2021_Berechnung"/>
+      <sheetName val="A1_2021_bearbeitet"/>
+      <sheetName val="A1_2020_Rohdaten"/>
+      <sheetName val="2021_rohdaten"/>
+      <sheetName val="2022_Rohdaten"/>
+      <sheetName val="2023_Rohdaten"/>
+      <sheetName val="2024_Rohdaten"/>
+      <sheetName val="2025_Rohdaten"/>
+      <sheetName val="CSV_Vorbereitung_Anzahl"/>
+      <sheetName val="CSV_Anzahl_Export"/>
+      <sheetName val="CSV_Vorbereitung_Veränderung"/>
+      <sheetName val="CSV_Veränderung_Export"/>
+      <sheetName val="CSV_Veränderung  gegenüber dem "/>
+      <sheetName val="CSV_VERÄ_GG_Vorjahr_Export"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>Indikator 1.1.1: Bevölkerung in Niedersachsen</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10">
+            <v>1</v>
+          </cell>
+          <cell r="C10">
+            <v>2</v>
+          </cell>
+          <cell r="D10">
+            <v>3</v>
+          </cell>
+          <cell r="E10">
+            <v>4</v>
+          </cell>
+          <cell r="F10">
+            <v>5</v>
+          </cell>
+          <cell r="G10">
+            <v>6</v>
+          </cell>
+          <cell r="H10">
+            <v>7</v>
+          </cell>
+          <cell r="I10">
+            <v>8</v>
+          </cell>
+          <cell r="J10">
+            <v>9</v>
+          </cell>
+          <cell r="K10">
+            <v>10</v>
+          </cell>
+          <cell r="L10">
+            <v>11</v>
+          </cell>
+          <cell r="M10">
+            <v>12</v>
+          </cell>
+          <cell r="N10">
+            <v>13</v>
+          </cell>
+          <cell r="O10">
+            <v>14</v>
+          </cell>
+          <cell r="P10">
+            <v>15</v>
+          </cell>
+          <cell r="Q10">
+            <v>16</v>
+          </cell>
+          <cell r="R10">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11" t="str">
+            <v>Braunschweig, Stadt</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="B12" t="str">
+            <v>Salzgitter, Stadt</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="B13" t="str">
+            <v>Wolfsburg, Stadt</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="B14" t="str">
+            <v>Gifhorn</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="B15" t="str">
+            <v>Goslar</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="B16" t="str">
+            <v>Helmstedt</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="B17" t="str">
+            <v>Northeim</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="B18" t="str">
+            <v>Peine</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="B19" t="str">
+            <v>Wolfenbüttel</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="B20" t="str">
+            <v>Göttingen</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="B21" t="str">
+            <v>Statistische Region Braunschweig</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22" t="str">
+            <v>Region Hannover</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23" t="str">
+            <v>dav. Hannover, Lhst.</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="B24" t="str">
+            <v>dav. Hannover, Umland</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="B25" t="str">
+            <v>Diepholz</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="B26" t="str">
+            <v>Hameln-Pyrmont</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="B27" t="str">
+            <v>Hildesheim</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="B28" t="str">
+            <v>Holzminden</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="B29" t="str">
+            <v>Nienburg (Weser)</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="B30" t="str">
+            <v>Schaumburg</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="B31" t="str">
+            <v>Statistische Region Hannover</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="B32" t="str">
+            <v>Celle</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="B33" t="str">
+            <v>Cuxhaven</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="B34" t="str">
+            <v>Harburg</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="B35" t="str">
+            <v>Lüchow-Dannenberg</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="B36" t="str">
+            <v>Lüneburg</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="B37" t="str">
+            <v>Osterholz</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="B38" t="str">
+            <v>Rotenburg (Wümme)</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="B39" t="str">
+            <v>Heidekreis</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="B40" t="str">
+            <v>Stade</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="B41" t="str">
+            <v>Uelzen</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="B42" t="str">
+            <v>Verden</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="B43" t="str">
+            <v>Statistische Region Lüneburg</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="B44" t="str">
+            <v>Delmenhorst, Stadt</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="B45" t="str">
+            <v>Emden, Stadt</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="B46" t="str">
+            <v>Oldenburg (Oldb), Stadt</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="B47" t="str">
+            <v>Osnabrück, Stadt</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="B48" t="str">
+            <v>Wilhelmshaven, Stadt</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="B49" t="str">
+            <v>Ammerland</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="B50" t="str">
+            <v>Aurich</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="B51" t="str">
+            <v>Cloppenburg</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="B52" t="str">
+            <v>Emsland</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="B53" t="str">
+            <v>Friesland</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="B54" t="str">
+            <v>Grafschaft Bentheim</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="B55" t="str">
+            <v>Leer</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="B56" t="str">
+            <v>Oldenburg</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="B57" t="str">
+            <v>Osnabrück</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="B58" t="str">
+            <v>Vechta</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="B59" t="str">
+            <v>Wesermarsch</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="B60" t="str">
+            <v>Wittmund</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="B61" t="str">
+            <v>Statistische Region Weser-Ems</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="B62" t="str">
+            <v>Niedersachsen</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="B67" t="str">
+            <v>Quelle: Bevölkerungsfortschreibung</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 – 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -552,39 +769,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 – 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -636,7 +853,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -688,7 +905,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 – 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -747,13 +964,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -762,6 +972,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -826,4559 +1043,4595 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{017B5BDD-0A11-45EA-8564-DA0C056DBCB1}">
-  <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:AA72"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7234B224-4812-4C46-8616-AB6BA8B9CBFD}">
+  <dimension ref="B1:AA72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" customWidth="1"/>
     <col min="2" max="2" width="11.7109375" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="26.7109375" customWidth="1"/>
+    <col min="24" max="27" width="11.42578125" style="21"/>
+    <col min="28" max="28" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>69</v>
-      </c>
+    <row r="1" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="2" t="str">
+        <f>[1]A1_2021_Berechnung!B3</f>
+        <v>Indikator 1.1.1: Bevölkerung in Niedersachsen</v>
+      </c>
+    </row>
+    <row r="4" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
-      <c r="S7" s="23"/>
-      <c r="T7" s="23"/>
-      <c r="U7" s="23"/>
-      <c r="V7" s="23"/>
-      <c r="W7" s="23"/>
-      <c r="X7" s="24"/>
+    </row>
+    <row r="7" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="5"/>
+      <c r="X7" s="6"/>
       <c r="Y7" s="22" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z7" s="23"/>
       <c r="AA7" s="23"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="C8" s="20"/>
-      <c r="D8" s="13">
+    <row r="8" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="C8" s="7"/>
+      <c r="D8" s="8">
         <v>2005</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="8">
         <v>2006</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="8">
         <v>2007</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="8">
         <v>2008</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="9">
         <v>2009</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="9">
         <v>2010</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="9">
         <v>2011</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="9">
         <v>2012</v>
       </c>
-      <c r="L8" s="14">
+      <c r="L8" s="9">
         <v>2013</v>
       </c>
-      <c r="M8" s="14">
+      <c r="M8" s="9">
         <v>2014</v>
       </c>
-      <c r="N8" s="14">
+      <c r="N8" s="9">
         <v>2015</v>
       </c>
-      <c r="O8" s="14">
+      <c r="O8" s="9">
         <v>2016</v>
       </c>
-      <c r="P8" s="14">
+      <c r="P8" s="9">
         <v>2017</v>
       </c>
-      <c r="Q8" s="14">
+      <c r="Q8" s="9">
         <v>2018</v>
       </c>
-      <c r="R8" s="14">
+      <c r="R8" s="9">
         <v>2019</v>
       </c>
-      <c r="S8" s="14">
+      <c r="S8" s="9">
         <v>2020</v>
       </c>
-      <c r="T8" s="14">
+      <c r="T8" s="9">
         <v>2021</v>
       </c>
-      <c r="U8" s="14">
+      <c r="U8" s="9">
         <v>2022</v>
       </c>
-      <c r="V8" s="14">
+      <c r="V8" s="9">
         <v>2023</v>
       </c>
-      <c r="W8" s="14">
+      <c r="W8" s="9">
         <v>2024</v>
       </c>
-      <c r="X8" s="14">
+      <c r="X8" s="24">
         <v>2025</v>
       </c>
-      <c r="Y8" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z8" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA8" s="15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="C9" s="21"/>
-      <c r="D9" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
-      <c r="S9" s="23"/>
-      <c r="T9" s="23"/>
-      <c r="U9" s="23"/>
-      <c r="V9" s="23"/>
-      <c r="W9" s="23"/>
-      <c r="X9" s="24"/>
+      <c r="Y8" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z8" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA8" s="25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="C9" s="10"/>
+      <c r="D9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="5"/>
+      <c r="U9" s="5"/>
+      <c r="V9" s="5"/>
+      <c r="W9" s="5"/>
+      <c r="X9" s="6"/>
       <c r="Y9" s="22" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Z9" s="23"/>
       <c r="AA9" s="23"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="C10" s="16">
+    <row r="10" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="C10" s="11">
+        <f>[1]A1_2021_Berechnung!B10</f>
         <v>1</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="11">
+        <f>[1]A1_2021_Berechnung!C10</f>
         <v>2</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="11">
+        <f>[1]A1_2021_Berechnung!D10</f>
         <v>3</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="11">
+        <f>[1]A1_2021_Berechnung!E10</f>
         <v>4</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="11">
+        <f>[1]A1_2021_Berechnung!F10</f>
         <v>5</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="11">
+        <f>[1]A1_2021_Berechnung!G10</f>
         <v>6</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="11">
+        <f>[1]A1_2021_Berechnung!H10</f>
         <v>7</v>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="11">
+        <f>[1]A1_2021_Berechnung!I10</f>
         <v>8</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="11">
+        <f>[1]A1_2021_Berechnung!J10</f>
         <v>9</v>
       </c>
-      <c r="L10" s="16">
+      <c r="L10" s="11">
+        <f>[1]A1_2021_Berechnung!K10</f>
         <v>10</v>
       </c>
-      <c r="M10" s="16">
+      <c r="M10" s="11">
+        <f>[1]A1_2021_Berechnung!L10</f>
         <v>11</v>
       </c>
-      <c r="N10" s="16">
+      <c r="N10" s="11">
+        <f>[1]A1_2021_Berechnung!M10</f>
         <v>12</v>
       </c>
-      <c r="O10" s="16">
+      <c r="O10" s="11">
+        <f>[1]A1_2021_Berechnung!N10</f>
         <v>13</v>
       </c>
-      <c r="P10" s="16">
+      <c r="P10" s="11">
+        <f>[1]A1_2021_Berechnung!O10</f>
         <v>14</v>
       </c>
-      <c r="Q10" s="16">
+      <c r="Q10" s="11">
+        <f>[1]A1_2021_Berechnung!P10</f>
         <v>15</v>
       </c>
-      <c r="R10" s="16">
+      <c r="R10" s="11">
+        <f>[1]A1_2021_Berechnung!Q10</f>
         <v>16</v>
       </c>
-      <c r="S10" s="16">
+      <c r="S10" s="11">
+        <f>[1]A1_2021_Berechnung!R10</f>
         <v>17</v>
       </c>
-      <c r="T10" s="16">
+      <c r="T10" s="11">
         <v>18</v>
       </c>
-      <c r="U10" s="16">
+      <c r="U10" s="11">
         <v>19</v>
       </c>
-      <c r="V10" s="16">
+      <c r="V10" s="11">
         <v>20</v>
       </c>
-      <c r="W10" s="16">
+      <c r="W10" s="11">
         <v>21</v>
       </c>
-      <c r="X10" s="16">
+      <c r="X10" s="26">
         <v>22</v>
       </c>
-      <c r="Y10" s="16">
+      <c r="Y10" s="26">
         <v>23</v>
       </c>
-      <c r="Z10" s="16">
+      <c r="Z10" s="26">
         <v>24</v>
       </c>
-      <c r="AA10" s="16">
+      <c r="AA10" s="26">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="3">
+    <row r="11" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="12">
         <v>101</v>
       </c>
-      <c r="C11" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="9">
+      <c r="C11" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B11</f>
+        <v>Braunschweig, Stadt</v>
+      </c>
+      <c r="D11" s="14">
         <v>245273</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="14">
         <v>245467</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="14">
         <v>245810</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="14">
         <v>246012</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="14">
         <v>247400</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="14">
         <v>248867</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="14">
         <v>243829</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K11" s="14">
         <v>245798</v>
       </c>
-      <c r="L11" s="9">
+      <c r="L11" s="14">
         <v>247227</v>
       </c>
-      <c r="M11" s="9">
+      <c r="M11" s="14">
         <v>248502</v>
       </c>
-      <c r="N11" s="9">
+      <c r="N11" s="14">
         <v>251364</v>
       </c>
-      <c r="O11" s="9">
+      <c r="O11" s="14">
         <v>248667</v>
       </c>
-      <c r="P11" s="9">
+      <c r="P11" s="14">
         <v>248023</v>
       </c>
-      <c r="Q11" s="9">
+      <c r="Q11" s="14">
         <v>248292</v>
       </c>
-      <c r="R11" s="9">
+      <c r="R11" s="14">
         <v>249406</v>
       </c>
-      <c r="S11" s="9">
+      <c r="S11" s="14">
         <v>248561</v>
       </c>
-      <c r="T11" s="9">
+      <c r="T11" s="14">
         <v>248823</v>
       </c>
-      <c r="U11" s="9">
+      <c r="U11" s="14">
         <v>253194</v>
       </c>
-      <c r="V11" s="9">
+      <c r="V11" s="14">
         <v>253527</v>
       </c>
-      <c r="W11" s="9">
+      <c r="W11" s="14">
         <v>252962</v>
       </c>
-      <c r="X11" s="9">
+      <c r="X11" s="27">
         <v>252811</v>
       </c>
-      <c r="Y11" s="10">
-        <v>3.073310148283749</v>
-      </c>
-      <c r="Z11" s="10">
-        <v>1.6810977370446698</v>
-      </c>
-      <c r="AA11" s="10">
-        <v>-5.9728413716175321E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="3">
+      <c r="Y11" s="28">
+        <v>3.0733101482837526</v>
+      </c>
+      <c r="Z11" s="28">
+        <v>1.7098418496867964</v>
+      </c>
+      <c r="AA11" s="28">
+        <v>-5.9692760177412652E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="12">
         <v>102</v>
       </c>
-      <c r="C12" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="9">
+      <c r="C12" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B12</f>
+        <v>Salzgitter, Stadt</v>
+      </c>
+      <c r="D12" s="14">
         <v>107726</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="14">
         <v>106665</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="14">
         <v>105320</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="14">
         <v>104423</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="14">
         <v>103446</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="14">
         <v>102394</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="14">
         <v>98588</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="14">
         <v>98095</v>
       </c>
-      <c r="L12" s="9">
+      <c r="L12" s="14">
         <v>98197</v>
       </c>
-      <c r="M12" s="9">
+      <c r="M12" s="14">
         <v>98966</v>
       </c>
-      <c r="N12" s="9">
+      <c r="N12" s="14">
         <v>101079</v>
       </c>
-      <c r="O12" s="9">
+      <c r="O12" s="14">
         <v>103668</v>
       </c>
-      <c r="P12" s="9">
+      <c r="P12" s="14">
         <v>104548</v>
       </c>
-      <c r="Q12" s="9">
+      <c r="Q12" s="14">
         <v>104948</v>
       </c>
-      <c r="R12" s="9">
+      <c r="R12" s="14">
         <v>104291</v>
       </c>
-      <c r="S12" s="9">
+      <c r="S12" s="14">
         <v>103866</v>
       </c>
-      <c r="T12" s="9">
+      <c r="T12" s="14">
         <v>103694</v>
       </c>
-      <c r="U12" s="9">
+      <c r="U12" s="14">
         <v>104564</v>
       </c>
-      <c r="V12" s="9">
+      <c r="V12" s="14">
         <v>105056</v>
       </c>
-      <c r="W12" s="9">
+      <c r="W12" s="14">
         <v>104970</v>
       </c>
-      <c r="X12" s="9">
+      <c r="X12" s="27">
         <v>104433</v>
       </c>
-      <c r="Y12" s="10">
-        <v>-3.056829363384884</v>
-      </c>
-      <c r="Z12" s="10">
-        <v>0.54293183189221794</v>
-      </c>
-      <c r="AA12" s="10">
-        <v>-0.51420527994024878</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="3">
+      <c r="Y12" s="28">
+        <v>-3.0568293633848782</v>
+      </c>
+      <c r="Z12" s="28">
+        <v>0.54589567327133182</v>
+      </c>
+      <c r="AA12" s="28">
+        <v>-0.5115747356387601</v>
+      </c>
+    </row>
+    <row r="13" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="12">
         <v>103</v>
       </c>
-      <c r="C13" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="9">
+      <c r="C13" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B13</f>
+        <v>Wolfsburg, Stadt</v>
+      </c>
+      <c r="D13" s="14">
         <v>121199</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="14">
         <v>120493</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="14">
         <v>120009</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="14">
         <v>120538</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="14">
         <v>121109</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="14">
         <v>121451</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="14">
         <v>120889</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="14">
         <v>121758</v>
       </c>
-      <c r="L13" s="9">
+      <c r="L13" s="14">
         <v>122457</v>
       </c>
-      <c r="M13" s="9">
+      <c r="M13" s="14">
         <v>123027</v>
       </c>
-      <c r="N13" s="9">
+      <c r="N13" s="14">
         <v>124045</v>
       </c>
-      <c r="O13" s="9">
+      <c r="O13" s="14">
         <v>123909</v>
       </c>
-      <c r="P13" s="9">
+      <c r="P13" s="14">
         <v>123914</v>
       </c>
-      <c r="Q13" s="9">
+      <c r="Q13" s="14">
         <v>124151</v>
       </c>
-      <c r="R13" s="9">
+      <c r="R13" s="14">
         <v>124371</v>
       </c>
-      <c r="S13" s="9">
+      <c r="S13" s="14">
         <v>123840</v>
       </c>
-      <c r="T13" s="9">
+      <c r="T13" s="14">
         <v>123949</v>
       </c>
-      <c r="U13" s="9">
+      <c r="U13" s="14">
         <v>127990</v>
       </c>
-      <c r="V13" s="9">
+      <c r="V13" s="14">
         <v>129347</v>
       </c>
-      <c r="W13" s="9">
+      <c r="W13" s="14">
         <v>129560</v>
       </c>
-      <c r="X13" s="9">
+      <c r="X13" s="27">
         <v>129813</v>
       </c>
-      <c r="Y13" s="10">
-        <v>7.1073193673215123</v>
-      </c>
-      <c r="Z13" s="10">
-        <v>4.6012340828730558</v>
-      </c>
-      <c r="AA13" s="10">
-        <v>0.19489573463366536</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="3">
+      <c r="Y13" s="28">
+        <v>7.1073193673215087</v>
+      </c>
+      <c r="Z13" s="28">
+        <v>4.8231589147286797</v>
+      </c>
+      <c r="AA13" s="28">
+        <v>0.19527631985179994</v>
+      </c>
+    </row>
+    <row r="14" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="12">
         <v>151</v>
       </c>
-      <c r="C14" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="9">
+      <c r="C14" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B14</f>
+        <v>Gifhorn</v>
+      </c>
+      <c r="D14" s="14">
         <v>175298</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="14">
         <v>174974</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="14">
         <v>174401</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="14">
         <v>173765</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="14">
         <v>173223</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="14">
         <v>172643</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="14">
         <v>170865</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K14" s="14">
         <v>171015</v>
       </c>
-      <c r="L14" s="9">
+      <c r="L14" s="14">
         <v>171475</v>
       </c>
-      <c r="M14" s="9">
+      <c r="M14" s="14">
         <v>172541</v>
       </c>
-      <c r="N14" s="9">
+      <c r="N14" s="14">
         <v>174205</v>
       </c>
-      <c r="O14" s="9">
+      <c r="O14" s="14">
         <v>174749</v>
       </c>
-      <c r="P14" s="9">
+      <c r="P14" s="14">
         <v>175079</v>
       </c>
-      <c r="Q14" s="9">
+      <c r="Q14" s="14">
         <v>175920</v>
       </c>
-      <c r="R14" s="9">
+      <c r="R14" s="14">
         <v>176523</v>
       </c>
-      <c r="S14" s="9">
+      <c r="S14" s="14">
         <v>177227</v>
       </c>
-      <c r="T14" s="9">
+      <c r="T14" s="14">
         <v>177919</v>
       </c>
-      <c r="U14" s="9">
+      <c r="U14" s="14">
         <v>175361</v>
       </c>
-      <c r="V14" s="9">
+      <c r="V14" s="14">
         <v>175876</v>
       </c>
-      <c r="W14" s="9">
+      <c r="W14" s="14">
         <v>175943</v>
       </c>
-      <c r="X14" s="9">
+      <c r="X14" s="27">
         <v>175518</v>
       </c>
-      <c r="Y14" s="10">
-        <v>0.12550057616173602</v>
-      </c>
-      <c r="Z14" s="10">
-        <v>-0.97368930821910005</v>
-      </c>
-      <c r="AA14" s="10">
-        <v>-0.2421404072516779</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="3">
+      <c r="Y14" s="28">
+        <v>0.12550057616174115</v>
+      </c>
+      <c r="Z14" s="28">
+        <v>-0.96430002200567344</v>
+      </c>
+      <c r="AA14" s="28">
+        <v>-0.24155550377111012</v>
+      </c>
+    </row>
+    <row r="15" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="12">
         <v>153</v>
       </c>
-      <c r="C15" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="9">
+      <c r="C15" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B15</f>
+        <v>Goslar</v>
+      </c>
+      <c r="D15" s="14">
         <v>151452</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="14">
         <v>149656</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="14">
         <v>148091</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="14">
         <v>146187</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="14">
         <v>144680</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="14">
         <v>143014</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="14">
         <v>139575</v>
       </c>
-      <c r="K15" s="9">
+      <c r="K15" s="14">
         <v>138655</v>
       </c>
-      <c r="L15" s="9">
+      <c r="L15" s="14">
         <v>137833</v>
       </c>
-      <c r="M15" s="9">
+      <c r="M15" s="14">
         <v>137256</v>
       </c>
-      <c r="N15" s="9">
+      <c r="N15" s="14">
         <v>138236</v>
       </c>
-      <c r="O15" s="9">
+      <c r="O15" s="14">
         <v>137979</v>
       </c>
-      <c r="P15" s="9">
+      <c r="P15" s="14">
         <v>137563</v>
       </c>
-      <c r="Q15" s="9">
+      <c r="Q15" s="14">
         <v>137014</v>
       </c>
-      <c r="R15" s="9">
+      <c r="R15" s="14">
         <v>136292</v>
       </c>
-      <c r="S15" s="9">
+      <c r="S15" s="14">
         <v>134688</v>
       </c>
-      <c r="T15" s="9">
+      <c r="T15" s="14">
         <v>134050</v>
       </c>
-      <c r="U15" s="9">
+      <c r="U15" s="14">
         <v>127856</v>
       </c>
-      <c r="V15" s="9">
+      <c r="V15" s="14">
         <v>127712</v>
       </c>
-      <c r="W15" s="9">
+      <c r="W15" s="14">
         <v>126775</v>
       </c>
-      <c r="X15" s="9">
+      <c r="X15" s="27">
         <v>126082</v>
       </c>
-      <c r="Y15" s="10">
-        <v>-16.751181892612841</v>
-      </c>
-      <c r="Z15" s="10">
-        <v>-6.8257165971351981</v>
-      </c>
-      <c r="AA15" s="10">
-        <v>-0.54964229628337113</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="3">
+      <c r="Y15" s="28">
+        <v>-16.751181892612834</v>
+      </c>
+      <c r="Z15" s="28">
+        <v>-6.3895818484200504</v>
+      </c>
+      <c r="AA15" s="28">
+        <v>-0.54663774403471166</v>
+      </c>
+    </row>
+    <row r="16" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="12">
         <v>154</v>
       </c>
-      <c r="C16" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="9">
+      <c r="C16" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B16</f>
+        <v>Helmstedt</v>
+      </c>
+      <c r="D16" s="14">
         <v>97749</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="14">
         <v>96972</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="14">
         <v>95871</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="14">
         <v>94870</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="14">
         <v>93903</v>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="14">
         <v>92836</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="14">
         <v>90919</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="14">
         <v>90391</v>
       </c>
-      <c r="L16" s="9">
+      <c r="L16" s="14">
         <v>90423</v>
       </c>
-      <c r="M16" s="9">
+      <c r="M16" s="14">
         <v>90908</v>
       </c>
-      <c r="N16" s="9">
+      <c r="N16" s="14">
         <v>91500</v>
       </c>
-      <c r="O16" s="9">
+      <c r="O16" s="14">
         <v>92079</v>
       </c>
-      <c r="P16" s="9">
+      <c r="P16" s="14">
         <v>91720</v>
       </c>
-      <c r="Q16" s="9">
+      <c r="Q16" s="14">
         <v>91307</v>
       </c>
-      <c r="R16" s="9">
+      <c r="R16" s="14">
         <v>91297</v>
       </c>
-      <c r="S16" s="9">
+      <c r="S16" s="14">
         <v>91518</v>
       </c>
-      <c r="T16" s="9">
+      <c r="T16" s="14">
         <v>91379</v>
       </c>
-      <c r="U16" s="9">
+      <c r="U16" s="14">
         <v>90985</v>
       </c>
-      <c r="V16" s="9">
+      <c r="V16" s="14">
         <v>90692</v>
       </c>
-      <c r="W16" s="9">
+      <c r="W16" s="14">
         <v>90227</v>
       </c>
-      <c r="X16" s="9">
+      <c r="X16" s="27">
         <v>89771</v>
       </c>
-      <c r="Y16" s="10">
-        <v>-8.1617203245045982</v>
-      </c>
-      <c r="Z16" s="10">
-        <v>-1.9460627596885409</v>
-      </c>
-      <c r="AA16" s="10">
-        <v>-0.50795914047966495</v>
-      </c>
-    </row>
-    <row r="17" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="3">
+      <c r="Y16" s="28">
+        <v>-8.1617203245045999</v>
+      </c>
+      <c r="Z16" s="28">
+        <v>-1.9089140934023874</v>
+      </c>
+      <c r="AA16" s="28">
+        <v>-0.50539195584470065</v>
+      </c>
+    </row>
+    <row r="17" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="12">
         <v>155</v>
       </c>
-      <c r="C17" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="9">
+      <c r="C17" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B17</f>
+        <v>Northeim</v>
+      </c>
+      <c r="D17" s="14">
         <v>146690</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="14">
         <v>145488</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="14">
         <v>144044</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="14">
         <v>142321</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="14">
         <v>140553</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="14">
         <v>139060</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="14">
         <v>136516</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="14">
         <v>135418</v>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="14">
         <v>134661</v>
       </c>
-      <c r="M17" s="9">
+      <c r="M17" s="14">
         <v>133905</v>
       </c>
-      <c r="N17" s="9">
+      <c r="N17" s="14">
         <v>134896</v>
       </c>
-      <c r="O17" s="9">
+      <c r="O17" s="14">
         <v>133610</v>
       </c>
-      <c r="P17" s="9">
+      <c r="P17" s="14">
         <v>133046</v>
       </c>
-      <c r="Q17" s="9">
+      <c r="Q17" s="14">
         <v>132765</v>
       </c>
-      <c r="R17" s="9">
+      <c r="R17" s="14">
         <v>132285</v>
       </c>
-      <c r="S17" s="9">
+      <c r="S17" s="14">
         <v>131772</v>
       </c>
-      <c r="T17" s="9">
+      <c r="T17" s="14">
         <v>131765</v>
       </c>
-      <c r="U17" s="9">
+      <c r="U17" s="14">
         <v>126598</v>
       </c>
-      <c r="V17" s="9">
+      <c r="V17" s="14">
         <v>126310</v>
       </c>
-      <c r="W17" s="9">
+      <c r="W17" s="14">
         <v>125623</v>
       </c>
-      <c r="X17" s="9">
+      <c r="X17" s="27">
         <v>124692</v>
       </c>
-      <c r="Y17" s="10">
+      <c r="Y17" s="28">
         <v>-14.996250596496012</v>
       </c>
-      <c r="Z17" s="10">
-        <v>-5.6779905687614285</v>
-      </c>
-      <c r="AA17" s="10">
-        <v>-0.7466397202707471</v>
-      </c>
-    </row>
-    <row r="18" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="3">
+      <c r="Z17" s="28">
+        <v>-5.3729168563883007</v>
+      </c>
+      <c r="AA17" s="28">
+        <v>-0.74110632607086302</v>
+      </c>
+    </row>
+    <row r="18" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="12">
         <v>157</v>
       </c>
-      <c r="C18" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="9">
+      <c r="C18" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B18</f>
+        <v>Peine</v>
+      </c>
+      <c r="D18" s="14">
         <v>134581</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="14">
         <v>134178</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="14">
         <v>133560</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="14">
         <v>132613</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="14">
         <v>132066</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="14">
         <v>131481</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="14">
         <v>130165</v>
       </c>
-      <c r="K18" s="9">
+      <c r="K18" s="14">
         <v>130047</v>
       </c>
-      <c r="L18" s="9">
+      <c r="L18" s="14">
         <v>130147</v>
       </c>
-      <c r="M18" s="9">
+      <c r="M18" s="14">
         <v>130601</v>
       </c>
-      <c r="N18" s="9">
+      <c r="N18" s="14">
         <v>132320</v>
       </c>
-      <c r="O18" s="9">
+      <c r="O18" s="14">
         <v>132979</v>
       </c>
-      <c r="P18" s="9">
+      <c r="P18" s="14">
         <v>133368</v>
       </c>
-      <c r="Q18" s="9">
+      <c r="Q18" s="14">
         <v>133965</v>
       </c>
-      <c r="R18" s="9">
+      <c r="R18" s="14">
         <v>134801</v>
       </c>
-      <c r="S18" s="9">
+      <c r="S18" s="14">
         <v>135844</v>
       </c>
-      <c r="T18" s="9">
+      <c r="T18" s="14">
         <v>136960</v>
       </c>
-      <c r="U18" s="9">
+      <c r="U18" s="14">
         <v>136719</v>
       </c>
-      <c r="V18" s="9">
+      <c r="V18" s="14">
         <v>136983</v>
       </c>
-      <c r="W18" s="9">
+      <c r="W18" s="14">
         <v>137045</v>
       </c>
-      <c r="X18" s="9">
+      <c r="X18" s="27">
         <v>137149</v>
       </c>
-      <c r="Y18" s="10">
-        <v>1.9081445374904333</v>
-      </c>
-      <c r="Z18" s="10">
-        <v>0.95151987983871555</v>
-      </c>
-      <c r="AA18" s="10">
-        <v>7.582993678408155E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="3">
+      <c r="Y18" s="28">
+        <v>1.9081445374904291</v>
+      </c>
+      <c r="Z18" s="28">
+        <v>0.96066075792820982</v>
+      </c>
+      <c r="AA18" s="28">
+        <v>7.5887482213872204E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="12">
         <v>158</v>
       </c>
-      <c r="C19" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="9">
+      <c r="C19" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B19</f>
+        <v>Wolfenbüttel</v>
+      </c>
+      <c r="D19" s="14">
         <v>126460</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="14">
         <v>125412</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="14">
         <v>124652</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="14">
         <v>123663</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="14">
         <v>122806</v>
       </c>
-      <c r="I19" s="9">
+      <c r="I19" s="14">
         <v>122040</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="14">
         <v>120425</v>
       </c>
-      <c r="K19" s="9">
+      <c r="K19" s="14">
         <v>120117</v>
       </c>
-      <c r="L19" s="9">
+      <c r="L19" s="14">
         <v>119900</v>
       </c>
-      <c r="M19" s="9">
+      <c r="M19" s="14">
         <v>120035</v>
       </c>
-      <c r="N19" s="9">
+      <c r="N19" s="14">
         <v>120981</v>
       </c>
-      <c r="O19" s="9">
+      <c r="O19" s="14">
         <v>120904</v>
       </c>
-      <c r="P19" s="9">
+      <c r="P19" s="14">
         <v>120437</v>
       </c>
-      <c r="Q19" s="9">
+      <c r="Q19" s="14">
         <v>119960</v>
       </c>
-      <c r="R19" s="9">
+      <c r="R19" s="14">
         <v>119622</v>
       </c>
-      <c r="S19" s="9">
+      <c r="S19" s="14">
         <v>119361</v>
       </c>
-      <c r="T19" s="9">
+      <c r="T19" s="14">
         <v>119224</v>
       </c>
-      <c r="U19" s="9">
+      <c r="U19" s="14">
         <v>118296</v>
       </c>
-      <c r="V19" s="9">
+      <c r="V19" s="14">
         <v>118540</v>
       </c>
-      <c r="W19" s="9">
+      <c r="W19" s="14">
         <v>118290</v>
       </c>
-      <c r="X19" s="9">
+      <c r="X19" s="27">
         <v>117844</v>
       </c>
-      <c r="Y19" s="10">
-        <v>-6.8132215720385894</v>
-      </c>
-      <c r="Z19" s="10">
-        <v>-1.2872950680560742</v>
-      </c>
-      <c r="AA19" s="10">
-        <v>-0.37846644716744171</v>
-      </c>
-    </row>
-    <row r="20" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="3">
+      <c r="Y19" s="28">
+        <v>-6.8132215720385858</v>
+      </c>
+      <c r="Z19" s="28">
+        <v>-1.2709343923056906</v>
+      </c>
+      <c r="AA19" s="28">
+        <v>-0.37703947924592285</v>
+      </c>
+    </row>
+    <row r="20" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="12">
         <v>159</v>
       </c>
-      <c r="C20" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="9">
+      <c r="C20" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B20</f>
+        <v>Göttingen</v>
+      </c>
+      <c r="D20" s="14">
         <v>344007</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="14">
         <v>342471</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="14">
         <v>341560</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="14">
         <v>339257</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="14">
         <v>337534</v>
       </c>
-      <c r="I20" s="9">
+      <c r="I20" s="14">
         <v>335583</v>
       </c>
-      <c r="J20" s="9">
+      <c r="J20" s="14">
         <v>324197</v>
       </c>
-      <c r="K20" s="9">
+      <c r="K20" s="14">
         <v>323233</v>
       </c>
-      <c r="L20" s="9">
+      <c r="L20" s="14">
         <v>322616</v>
       </c>
-      <c r="M20" s="9">
+      <c r="M20" s="14">
         <v>324013</v>
       </c>
-      <c r="N20" s="9">
+      <c r="N20" s="14">
         <v>329538</v>
       </c>
-      <c r="O20" s="9">
+      <c r="O20" s="14">
         <v>327065</v>
       </c>
-      <c r="P20" s="9">
+      <c r="P20" s="14">
         <v>328036</v>
       </c>
-      <c r="Q20" s="9">
+      <c r="Q20" s="14">
         <v>328074</v>
       </c>
-      <c r="R20" s="9">
+      <c r="R20" s="14">
         <v>326041</v>
       </c>
-      <c r="S20" s="9">
+      <c r="S20" s="14">
         <v>323900</v>
       </c>
-      <c r="T20" s="9">
+      <c r="T20" s="14">
         <v>323661</v>
       </c>
-      <c r="U20" s="9">
+      <c r="U20" s="14">
         <v>328039</v>
       </c>
-      <c r="V20" s="9">
+      <c r="V20" s="14">
         <v>328657</v>
       </c>
-      <c r="W20" s="9">
+      <c r="W20" s="14">
         <v>328028</v>
       </c>
-      <c r="X20" s="9">
+      <c r="X20" s="27">
         <v>330943</v>
       </c>
-      <c r="Y20" s="10">
-        <v>-3.7975971419186236</v>
-      </c>
-      <c r="Z20" s="10">
-        <v>2.1281610428381925</v>
-      </c>
-      <c r="AA20" s="10">
-        <v>0.88081633393061642</v>
-      </c>
-    </row>
-    <row r="21" spans="2:27" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="5">
+      <c r="Y20" s="28">
+        <v>-3.7975971419186294</v>
+      </c>
+      <c r="Z20" s="28">
+        <v>2.1744365544921322</v>
+      </c>
+      <c r="AA20" s="28">
+        <v>0.88864365237114384</v>
+      </c>
+    </row>
+    <row r="21" spans="2:27" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="15">
         <v>1</v>
       </c>
-      <c r="C21" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="D21" s="11">
+      <c r="C21" s="16" t="str">
+        <f>[1]A1_2021_Berechnung!B21</f>
+        <v>Statistische Region Braunschweig</v>
+      </c>
+      <c r="D21" s="17">
         <v>1650435</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="17">
         <v>1641776</v>
       </c>
-      <c r="F21" s="11">
+      <c r="F21" s="17">
         <v>1633318</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="17">
         <v>1623649</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H21" s="17">
         <v>1616720</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="17">
         <v>1609369</v>
       </c>
-      <c r="J21" s="11">
+      <c r="J21" s="17">
         <v>1575968</v>
       </c>
-      <c r="K21" s="11">
+      <c r="K21" s="17">
         <v>1574527</v>
       </c>
-      <c r="L21" s="11">
+      <c r="L21" s="17">
         <v>1574936</v>
       </c>
-      <c r="M21" s="11">
+      <c r="M21" s="17">
         <v>1579754</v>
       </c>
-      <c r="N21" s="11">
+      <c r="N21" s="17">
         <v>1598164</v>
       </c>
-      <c r="O21" s="11">
+      <c r="O21" s="17">
         <v>1595609</v>
       </c>
-      <c r="P21" s="11">
+      <c r="P21" s="17">
         <v>1595734</v>
       </c>
-      <c r="Q21" s="11">
+      <c r="Q21" s="17">
         <v>1596396</v>
       </c>
-      <c r="R21" s="11">
+      <c r="R21" s="17">
         <v>1594929</v>
       </c>
-      <c r="S21" s="11">
+      <c r="S21" s="17">
         <v>1590577</v>
       </c>
-      <c r="T21" s="11">
+      <c r="T21" s="17">
         <v>1591424</v>
       </c>
-      <c r="U21" s="11">
+      <c r="U21" s="17">
         <v>1589602</v>
       </c>
-      <c r="V21" s="11">
+      <c r="V21" s="17">
         <v>1592700</v>
       </c>
-      <c r="W21" s="11">
+      <c r="W21" s="17">
         <v>1589423</v>
       </c>
-      <c r="X21" s="11">
+      <c r="X21" s="29">
         <v>1589056</v>
       </c>
-      <c r="Y21" s="10">
-        <v>-3.7189589411276422</v>
-      </c>
-      <c r="Z21" s="10">
-        <v>-9.5717205686898385E-2</v>
-      </c>
-      <c r="AA21" s="10">
-        <v>-2.3095473035563252E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="3">
+      <c r="Y21" s="28">
+        <v>-3.7189589411276387</v>
+      </c>
+      <c r="Z21" s="28">
+        <v>-9.5625675462429172E-2</v>
+      </c>
+      <c r="AA21" s="28">
+        <v>-2.3090140258446468E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="12">
         <v>241</v>
       </c>
-      <c r="C22" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" s="9">
+      <c r="C22" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B22</f>
+        <v>Region Hannover</v>
+      </c>
+      <c r="D22" s="14">
         <v>1128543</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="14">
         <v>1128772</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="14">
         <v>1130039</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G22" s="14">
         <v>1129797</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="14">
         <v>1130262</v>
       </c>
-      <c r="I22" s="9">
+      <c r="I22" s="14">
         <v>1132130</v>
       </c>
-      <c r="J22" s="9">
+      <c r="J22" s="14">
         <v>1106219</v>
       </c>
-      <c r="K22" s="9">
+      <c r="K22" s="14">
         <v>1112675</v>
       </c>
-      <c r="L22" s="9">
+      <c r="L22" s="14">
         <v>1119526</v>
       </c>
-      <c r="M22" s="9">
+      <c r="M22" s="14">
         <v>1128037</v>
       </c>
-      <c r="N22" s="9">
+      <c r="N22" s="14">
         <v>1144481</v>
       </c>
-      <c r="O22" s="9">
+      <c r="O22" s="14">
         <v>1148700</v>
       </c>
-      <c r="P22" s="9">
+      <c r="P22" s="14">
         <v>1152675</v>
       </c>
-      <c r="Q22" s="9">
+      <c r="Q22" s="14">
         <v>1157624</v>
       </c>
-      <c r="R22" s="9">
+      <c r="R22" s="14">
         <v>1157115</v>
       </c>
-      <c r="S22" s="9">
+      <c r="S22" s="14">
         <v>1155330</v>
       </c>
-      <c r="T22" s="9">
+      <c r="T22" s="14">
         <v>1157541</v>
       </c>
-      <c r="U22" s="9">
+      <c r="U22" s="14">
         <v>1134284</v>
       </c>
-      <c r="V22" s="9">
+      <c r="V22" s="14">
         <v>1138943</v>
       </c>
-      <c r="W22" s="9">
+      <c r="W22" s="14">
         <v>1140888</v>
       </c>
-      <c r="X22" s="9">
+      <c r="X22" s="27">
         <v>1141128</v>
       </c>
-      <c r="Y22" s="10">
-        <v>1.1151546728835322</v>
-      </c>
-      <c r="Z22" s="10">
-        <v>-1.2445580162786296</v>
-      </c>
-      <c r="AA22" s="10">
-        <v>2.1031821145392978E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="3">
+      <c r="Y22" s="28">
+        <v>1.1151546728835342</v>
+      </c>
+      <c r="Z22" s="28">
+        <v>-1.2292591727039053</v>
+      </c>
+      <c r="AA22" s="28">
+        <v>2.1036245450915203E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="12">
         <v>241001</v>
       </c>
-      <c r="C23" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="9">
+      <c r="C23" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B23</f>
+        <v>dav. Hannover, Lhst.</v>
+      </c>
+      <c r="D23" s="14">
         <v>515729</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="14">
         <v>516343</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="14">
         <v>518069</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="14">
         <v>519619</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="14">
         <v>520966</v>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="14">
         <v>522686</v>
       </c>
-      <c r="J23" s="9">
+      <c r="J23" s="14">
         <v>509485</v>
       </c>
-      <c r="K23" s="9">
+      <c r="K23" s="14">
         <v>514137</v>
       </c>
-      <c r="L23" s="9">
+      <c r="L23" s="14">
         <v>518386</v>
       </c>
-      <c r="M23" s="9">
+      <c r="M23" s="14">
         <v>523642</v>
       </c>
-      <c r="N23" s="9">
+      <c r="N23" s="14">
         <v>532163</v>
       </c>
-      <c r="O23" s="9">
+      <c r="O23" s="14">
         <v>532864</v>
       </c>
-      <c r="P23" s="9">
+      <c r="P23" s="14">
         <v>535061</v>
       </c>
-      <c r="Q23" s="9">
+      <c r="Q23" s="14">
         <v>538068</v>
       </c>
-      <c r="R23" s="9">
+      <c r="R23" s="14">
         <v>536925</v>
       </c>
-      <c r="S23" s="9">
+      <c r="S23" s="14">
         <v>534049</v>
       </c>
-      <c r="T23" s="9">
+      <c r="T23" s="14">
         <v>535932</v>
       </c>
-      <c r="U23" s="9">
+      <c r="U23" s="14">
         <v>516540</v>
       </c>
-      <c r="V23" s="9">
+      <c r="V23" s="14">
         <v>520290</v>
       </c>
-      <c r="W23" s="9">
+      <c r="W23" s="14">
         <v>522131</v>
       </c>
-      <c r="X23" s="9">
+      <c r="X23" s="27">
         <v>522803</v>
       </c>
-      <c r="Y23" s="10">
-        <v>1.3716506149547534</v>
-      </c>
-      <c r="Z23" s="10">
-        <v>-2.1510970671553147</v>
-      </c>
-      <c r="AA23" s="10">
-        <v>0.1285379005093697</v>
-      </c>
-    </row>
-    <row r="24" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="3">
+      <c r="Y23" s="28">
+        <v>1.3716506149547598</v>
+      </c>
+      <c r="Z23" s="28">
+        <v>-2.1057992805903609</v>
+      </c>
+      <c r="AA23" s="28">
+        <v>0.12870333307158432</v>
+      </c>
+    </row>
+    <row r="24" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="12">
         <v>241999</v>
       </c>
-      <c r="C24" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" s="9">
+      <c r="C24" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B24</f>
+        <v>dav. Hannover, Umland</v>
+      </c>
+      <c r="D24" s="14">
         <v>612814</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="14">
         <v>612429</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F24" s="14">
         <v>611970</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G24" s="14">
         <v>610178</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="14">
         <v>609296</v>
       </c>
-      <c r="I24" s="9">
+      <c r="I24" s="14">
         <v>609444</v>
       </c>
-      <c r="J24" s="9">
+      <c r="J24" s="14">
         <v>596734</v>
       </c>
-      <c r="K24" s="9">
+      <c r="K24" s="14">
         <v>598538</v>
       </c>
-      <c r="L24" s="9">
+      <c r="L24" s="14">
         <v>601140</v>
       </c>
-      <c r="M24" s="9">
+      <c r="M24" s="14">
         <v>604395</v>
       </c>
-      <c r="N24" s="9">
+      <c r="N24" s="14">
         <v>612318</v>
       </c>
-      <c r="O24" s="9">
+      <c r="O24" s="14">
         <v>615836</v>
       </c>
-      <c r="P24" s="9">
+      <c r="P24" s="14">
         <v>617614</v>
       </c>
-      <c r="Q24" s="9">
+      <c r="Q24" s="14">
         <v>619556</v>
       </c>
-      <c r="R24" s="9">
+      <c r="R24" s="14">
         <v>620190</v>
       </c>
-      <c r="S24" s="9">
+      <c r="S24" s="14">
         <v>621281</v>
       </c>
-      <c r="T24" s="9">
+      <c r="T24" s="14">
         <v>621609</v>
       </c>
-      <c r="U24" s="9">
+      <c r="U24" s="14">
         <v>617744</v>
       </c>
-      <c r="V24" s="9">
+      <c r="V24" s="14">
         <v>618653</v>
       </c>
-      <c r="W24" s="9">
+      <c r="W24" s="14">
         <v>618757</v>
       </c>
-      <c r="X24" s="9">
+      <c r="X24" s="27">
         <v>618325</v>
       </c>
-      <c r="Y24" s="10">
-        <v>0.89929407617972179</v>
-      </c>
-      <c r="Z24" s="10">
-        <v>-0.47806574212590464</v>
-      </c>
-      <c r="AA24" s="10">
-        <v>-6.9866170703109201E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="3">
+      <c r="Y24" s="28">
+        <v>0.89929407617972856</v>
+      </c>
+      <c r="Z24" s="28">
+        <v>-0.47579114764494079</v>
+      </c>
+      <c r="AA24" s="28">
+        <v>-6.9817391964861031E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="12">
         <v>251</v>
       </c>
-      <c r="C25" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="9">
+      <c r="C25" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B25</f>
+        <v>Diepholz</v>
+      </c>
+      <c r="D25" s="14">
         <v>215548</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E25" s="14">
         <v>215406</v>
       </c>
-      <c r="F25" s="9">
+      <c r="F25" s="14">
         <v>215142</v>
       </c>
-      <c r="G25" s="9">
+      <c r="G25" s="14">
         <v>214379</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="14">
         <v>213634</v>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="14">
         <v>213558</v>
       </c>
-      <c r="J25" s="9">
+      <c r="J25" s="14">
         <v>209745</v>
       </c>
-      <c r="K25" s="9">
+      <c r="K25" s="14">
         <v>209671</v>
       </c>
-      <c r="L25" s="9">
+      <c r="L25" s="14">
         <v>209955</v>
       </c>
-      <c r="M25" s="9">
+      <c r="M25" s="14">
         <v>211093</v>
       </c>
-      <c r="N25" s="9">
+      <c r="N25" s="14">
         <v>213976</v>
       </c>
-      <c r="O25" s="9">
+      <c r="O25" s="14">
         <v>215082</v>
       </c>
-      <c r="P25" s="9">
+      <c r="P25" s="14">
         <v>216012</v>
       </c>
-      <c r="Q25" s="9">
+      <c r="Q25" s="14">
         <v>216886</v>
       </c>
-      <c r="R25" s="9">
+      <c r="R25" s="14">
         <v>217089</v>
       </c>
-      <c r="S25" s="9">
+      <c r="S25" s="14">
         <v>218072</v>
       </c>
-      <c r="T25" s="9">
+      <c r="T25" s="14">
         <v>218839</v>
       </c>
-      <c r="U25" s="9">
+      <c r="U25" s="14">
         <v>219641</v>
       </c>
-      <c r="V25" s="9">
+      <c r="V25" s="14">
         <v>220743</v>
       </c>
-      <c r="W25" s="9">
+      <c r="W25" s="14">
         <v>221202</v>
       </c>
-      <c r="X25" s="9">
+      <c r="X25" s="27">
         <v>221384</v>
       </c>
-      <c r="Y25" s="10">
-        <v>2.7075175830905414</v>
-      </c>
-      <c r="Z25" s="10">
-        <v>1.4960430744769269</v>
-      </c>
-      <c r="AA25" s="10">
-        <v>8.2210096483937414E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="3">
+      <c r="Y25" s="28">
+        <v>2.7075175830905351</v>
+      </c>
+      <c r="Z25" s="28">
+        <v>1.5187644447705395</v>
+      </c>
+      <c r="AA25" s="28">
+        <v>8.2277737090990399E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="12">
         <v>252</v>
       </c>
-      <c r="C26" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="D26" s="9">
+      <c r="C26" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B26</f>
+        <v>Hameln-Pyrmont</v>
+      </c>
+      <c r="D26" s="14">
         <v>159840</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="14">
         <v>158658</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="14">
         <v>157867</v>
       </c>
-      <c r="G26" s="9">
+      <c r="G26" s="14">
         <v>156398</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="14">
         <v>155164</v>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" s="14">
         <v>154085</v>
       </c>
-      <c r="J26" s="9">
+      <c r="J26" s="14">
         <v>149513</v>
       </c>
-      <c r="K26" s="9">
+      <c r="K26" s="14">
         <v>148532</v>
       </c>
-      <c r="L26" s="9">
+      <c r="L26" s="14">
         <v>147755</v>
       </c>
-      <c r="M26" s="9">
+      <c r="M26" s="14">
         <v>147813</v>
       </c>
-      <c r="N26" s="9">
+      <c r="N26" s="14">
         <v>148281</v>
       </c>
-      <c r="O26" s="9">
+      <c r="O26" s="14">
         <v>148265</v>
       </c>
-      <c r="P26" s="9">
+      <c r="P26" s="14">
         <v>148296</v>
       </c>
-      <c r="Q26" s="9">
+      <c r="Q26" s="14">
         <v>148559</v>
       </c>
-      <c r="R26" s="9">
+      <c r="R26" s="14">
         <v>148549</v>
       </c>
-      <c r="S26" s="9">
+      <c r="S26" s="14">
         <v>148580</v>
       </c>
-      <c r="T26" s="9">
+      <c r="T26" s="14">
         <v>148963</v>
       </c>
-      <c r="U26" s="9">
+      <c r="U26" s="14">
         <v>150717</v>
       </c>
-      <c r="V26" s="9">
+      <c r="V26" s="14">
         <v>150535</v>
       </c>
-      <c r="W26" s="9">
+      <c r="W26" s="14">
         <v>150203</v>
       </c>
-      <c r="X26" s="9">
+      <c r="X26" s="27">
         <v>149773</v>
       </c>
-      <c r="Y26" s="10">
-        <v>-6.2981731731731729</v>
-      </c>
-      <c r="Z26" s="10">
-        <v>0.79653876199314966</v>
-      </c>
-      <c r="AA26" s="10">
-        <v>-0.28710114640155437</v>
-      </c>
-    </row>
-    <row r="27" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="3">
+      <c r="Y26" s="28">
+        <v>-6.2981731731731685</v>
+      </c>
+      <c r="Z26" s="28">
+        <v>0.80293444608965103</v>
+      </c>
+      <c r="AA26" s="28">
+        <v>-0.28627923543470501</v>
+      </c>
+    </row>
+    <row r="27" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="12">
         <v>254</v>
       </c>
-      <c r="C27" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" s="9">
+      <c r="C27" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B27</f>
+        <v>Hildesheim</v>
+      </c>
+      <c r="D27" s="14">
         <v>290643</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="14">
         <v>289984</v>
       </c>
-      <c r="F27" s="9">
+      <c r="F27" s="14">
         <v>288623</v>
       </c>
-      <c r="G27" s="9">
+      <c r="G27" s="14">
         <v>286663</v>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="14">
         <v>284551</v>
       </c>
-      <c r="I27" s="9">
+      <c r="I27" s="14">
         <v>282856</v>
       </c>
-      <c r="J27" s="9">
+      <c r="J27" s="14">
         <v>276383</v>
       </c>
-      <c r="K27" s="9">
+      <c r="K27" s="14">
         <v>275330</v>
       </c>
-      <c r="L27" s="9">
+      <c r="L27" s="14">
         <v>274519</v>
       </c>
-      <c r="M27" s="9">
+      <c r="M27" s="14">
         <v>274554</v>
       </c>
-      <c r="N27" s="9">
+      <c r="N27" s="14">
         <v>277055</v>
       </c>
-      <c r="O27" s="9">
+      <c r="O27" s="14">
         <v>277300</v>
       </c>
-      <c r="P27" s="9">
+      <c r="P27" s="14">
         <v>276640</v>
       </c>
-      <c r="Q27" s="9">
+      <c r="Q27" s="14">
         <v>276594</v>
       </c>
-      <c r="R27" s="9">
+      <c r="R27" s="14">
         <v>275817</v>
       </c>
-      <c r="S27" s="9">
+      <c r="S27" s="14">
         <v>275464</v>
       </c>
-      <c r="T27" s="9">
+      <c r="T27" s="14">
         <v>274773</v>
       </c>
-      <c r="U27" s="9">
+      <c r="U27" s="14">
         <v>268062</v>
       </c>
-      <c r="V27" s="9">
+      <c r="V27" s="14">
         <v>268318</v>
       </c>
-      <c r="W27" s="9">
+      <c r="W27" s="14">
         <v>267506</v>
       </c>
-      <c r="X27" s="9">
+      <c r="X27" s="27">
         <v>266613</v>
       </c>
-      <c r="Y27" s="10">
-        <v>-8.2678750219341257</v>
-      </c>
-      <c r="Z27" s="10">
-        <v>-3.3197931083630579</v>
-      </c>
-      <c r="AA27" s="10">
-        <v>-0.33494240715944085</v>
-      </c>
-    </row>
-    <row r="28" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="3">
+      <c r="Y27" s="28">
+        <v>-8.267875021934131</v>
+      </c>
+      <c r="Z27" s="28">
+        <v>-3.213124037986816</v>
+      </c>
+      <c r="AA27" s="28">
+        <v>-0.33382428805334996</v>
+      </c>
+    </row>
+    <row r="28" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="12">
         <v>255</v>
       </c>
-      <c r="C28" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D28" s="9">
+      <c r="C28" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B28</f>
+        <v>Holzminden</v>
+      </c>
+      <c r="D28" s="14">
         <v>77918</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="14">
         <v>76888</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="14">
         <v>76103</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="14">
         <v>75092</v>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="14">
         <v>74094</v>
       </c>
-      <c r="I28" s="9">
+      <c r="I28" s="14">
         <v>73240</v>
       </c>
-      <c r="J28" s="9">
+      <c r="J28" s="14">
         <v>73155</v>
       </c>
-      <c r="K28" s="9">
+      <c r="K28" s="14">
         <v>72459</v>
       </c>
-      <c r="L28" s="9">
+      <c r="L28" s="14">
         <v>71877</v>
       </c>
-      <c r="M28" s="9">
+      <c r="M28" s="14">
         <v>71438</v>
       </c>
-      <c r="N28" s="9">
+      <c r="N28" s="14">
         <v>71659</v>
       </c>
-      <c r="O28" s="9">
+      <c r="O28" s="14">
         <v>71510</v>
       </c>
-      <c r="P28" s="9">
+      <c r="P28" s="14">
         <v>71144</v>
       </c>
-      <c r="Q28" s="9">
+      <c r="Q28" s="14">
         <v>70975</v>
       </c>
-      <c r="R28" s="9">
+      <c r="R28" s="14">
         <v>70458</v>
       </c>
-      <c r="S28" s="9">
+      <c r="S28" s="14">
         <v>70207</v>
       </c>
-      <c r="T28" s="9">
+      <c r="T28" s="14">
         <v>69862</v>
       </c>
-      <c r="U28" s="9">
+      <c r="U28" s="14">
         <v>66288</v>
       </c>
-      <c r="V28" s="9">
+      <c r="V28" s="14">
         <v>66088</v>
       </c>
-      <c r="W28" s="9">
+      <c r="W28" s="14">
         <v>65581</v>
       </c>
-      <c r="X28" s="9">
+      <c r="X28" s="27">
         <v>65271</v>
       </c>
-      <c r="Y28" s="10">
-        <v>-16.231166097692444</v>
-      </c>
-      <c r="Z28" s="10">
-        <v>-7.5623171086700065</v>
-      </c>
-      <c r="AA28" s="10">
-        <v>-0.47494293024467221</v>
-      </c>
-    </row>
-    <row r="29" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="3">
+      <c r="Y28" s="28">
+        <v>-16.231166097692451</v>
+      </c>
+      <c r="Z28" s="28">
+        <v>-7.0306379705727409</v>
+      </c>
+      <c r="AA28" s="28">
+        <v>-0.47269788505816734</v>
+      </c>
+    </row>
+    <row r="29" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="12">
         <v>256</v>
       </c>
-      <c r="C29" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D29" s="9">
+      <c r="C29" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B29</f>
+        <v>Nienburg (Weser)</v>
+      </c>
+      <c r="D29" s="14">
         <v>125870</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="14">
         <v>125436</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="14">
         <v>124895</v>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="14">
         <v>123881</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="14">
         <v>122989</v>
       </c>
-      <c r="I29" s="9">
+      <c r="I29" s="14">
         <v>122206</v>
       </c>
-      <c r="J29" s="9">
+      <c r="J29" s="14">
         <v>121390</v>
       </c>
-      <c r="K29" s="9">
+      <c r="K29" s="14">
         <v>120225</v>
       </c>
-      <c r="L29" s="9">
+      <c r="L29" s="14">
         <v>119848</v>
       </c>
-      <c r="M29" s="9">
+      <c r="M29" s="14">
         <v>119631</v>
       </c>
-      <c r="N29" s="9">
+      <c r="N29" s="14">
         <v>120632</v>
       </c>
-      <c r="O29" s="9">
+      <c r="O29" s="14">
         <v>121503</v>
       </c>
-      <c r="P29" s="9">
+      <c r="P29" s="14">
         <v>121470</v>
       </c>
-      <c r="Q29" s="9">
+      <c r="Q29" s="14">
         <v>121386</v>
       </c>
-      <c r="R29" s="9">
+      <c r="R29" s="14">
         <v>121390</v>
       </c>
-      <c r="S29" s="9">
+      <c r="S29" s="14">
         <v>121645</v>
       </c>
-      <c r="T29" s="9">
+      <c r="T29" s="14">
         <v>121773</v>
       </c>
-      <c r="U29" s="9">
+      <c r="U29" s="14">
         <v>121295</v>
       </c>
-      <c r="V29" s="9">
+      <c r="V29" s="14">
         <v>121723</v>
       </c>
-      <c r="W29" s="9">
+      <c r="W29" s="14">
         <v>121468</v>
       </c>
-      <c r="X29" s="9">
+      <c r="X29" s="27">
         <v>121159</v>
       </c>
-      <c r="Y29" s="10">
-        <v>-3.742750456820529</v>
-      </c>
-      <c r="Z29" s="10">
-        <v>-0.40112579337894833</v>
-      </c>
-      <c r="AA29" s="10">
-        <v>-0.25503676986439305</v>
-      </c>
-    </row>
-    <row r="30" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="3">
+      <c r="Y29" s="28">
+        <v>-3.7427504568205308</v>
+      </c>
+      <c r="Z29" s="28">
+        <v>-0.39952320276213982</v>
+      </c>
+      <c r="AA29" s="28">
+        <v>-0.25438798695952869</v>
+      </c>
+    </row>
+    <row r="30" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="12">
         <v>257</v>
       </c>
-      <c r="C30" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D30" s="9">
+      <c r="C30" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B30</f>
+        <v>Schaumburg</v>
+      </c>
+      <c r="D30" s="14">
         <v>165557</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="14">
         <v>165109</v>
       </c>
-      <c r="F30" s="9">
+      <c r="F30" s="14">
         <v>164172</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="14">
         <v>162971</v>
       </c>
-      <c r="H30" s="9">
+      <c r="H30" s="14">
         <v>161746</v>
       </c>
-      <c r="I30" s="9">
+      <c r="I30" s="14">
         <v>160636</v>
       </c>
-      <c r="J30" s="9">
+      <c r="J30" s="14">
         <v>157026</v>
       </c>
-      <c r="K30" s="9">
+      <c r="K30" s="14">
         <v>156039</v>
       </c>
-      <c r="L30" s="9">
+      <c r="L30" s="14">
         <v>155599</v>
       </c>
-      <c r="M30" s="9">
+      <c r="M30" s="14">
         <v>155847</v>
       </c>
-      <c r="N30" s="9">
+      <c r="N30" s="14">
         <v>156206</v>
       </c>
-      <c r="O30" s="9">
+      <c r="O30" s="14">
         <v>157616</v>
       </c>
-      <c r="P30" s="9">
+      <c r="P30" s="14">
         <v>157883</v>
       </c>
-      <c r="Q30" s="9">
+      <c r="Q30" s="14">
         <v>157781</v>
       </c>
-      <c r="R30" s="9">
+      <c r="R30" s="14">
         <v>157820</v>
       </c>
-      <c r="S30" s="9">
+      <c r="S30" s="14">
         <v>158406</v>
       </c>
-      <c r="T30" s="9">
+      <c r="T30" s="14">
         <v>158108</v>
       </c>
-      <c r="U30" s="9">
+      <c r="U30" s="14">
         <v>156747</v>
       </c>
-      <c r="V30" s="9">
+      <c r="V30" s="14">
         <v>157051</v>
       </c>
-      <c r="W30" s="9">
+      <c r="W30" s="14">
         <v>156841</v>
       </c>
-      <c r="X30" s="9">
+      <c r="X30" s="27">
         <v>156077</v>
       </c>
-      <c r="Y30" s="10">
-        <v>-5.7261245371684675</v>
-      </c>
-      <c r="Z30" s="10">
-        <v>-1.4922121773227317</v>
-      </c>
-      <c r="AA30" s="10">
-        <v>-0.48950197658847877</v>
-      </c>
-    </row>
-    <row r="31" spans="2:27" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="5">
+      <c r="Y30" s="28">
+        <v>-5.7261245371684737</v>
+      </c>
+      <c r="Z30" s="28">
+        <v>-1.4702725906847007</v>
+      </c>
+      <c r="AA30" s="28">
+        <v>-0.48711752666713437</v>
+      </c>
+    </row>
+    <row r="31" spans="2:27" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="15">
         <v>2</v>
       </c>
-      <c r="C31" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="D31" s="11">
+      <c r="C31" s="16" t="str">
+        <f>[1]A1_2021_Berechnung!B31</f>
+        <v>Statistische Region Hannover</v>
+      </c>
+      <c r="D31" s="17">
         <v>2163919</v>
       </c>
-      <c r="E31" s="11">
+      <c r="E31" s="17">
         <v>2160253</v>
       </c>
-      <c r="F31" s="11">
+      <c r="F31" s="17">
         <v>2156841</v>
       </c>
-      <c r="G31" s="11">
+      <c r="G31" s="17">
         <v>2149181</v>
       </c>
-      <c r="H31" s="11">
+      <c r="H31" s="17">
         <v>2142440</v>
       </c>
-      <c r="I31" s="11">
+      <c r="I31" s="17">
         <v>2138711</v>
       </c>
-      <c r="J31" s="11">
+      <c r="J31" s="17">
         <v>2093431</v>
       </c>
-      <c r="K31" s="11">
+      <c r="K31" s="17">
         <v>2094931</v>
       </c>
-      <c r="L31" s="11">
+      <c r="L31" s="17">
         <v>2099079</v>
       </c>
-      <c r="M31" s="11">
+      <c r="M31" s="17">
         <v>2108413</v>
       </c>
-      <c r="N31" s="11">
+      <c r="N31" s="17">
         <v>2132290</v>
       </c>
-      <c r="O31" s="11">
+      <c r="O31" s="17">
         <v>2139976</v>
       </c>
-      <c r="P31" s="11">
+      <c r="P31" s="17">
         <v>2144120</v>
       </c>
-      <c r="Q31" s="11">
+      <c r="Q31" s="17">
         <v>2149805</v>
       </c>
-      <c r="R31" s="11">
+      <c r="R31" s="17">
         <v>2148238</v>
       </c>
-      <c r="S31" s="11">
+      <c r="S31" s="17">
         <v>2147704</v>
       </c>
-      <c r="T31" s="11">
+      <c r="T31" s="17">
         <v>2149859</v>
       </c>
-      <c r="U31" s="11">
+      <c r="U31" s="17">
         <v>2117034</v>
       </c>
-      <c r="V31" s="11">
+      <c r="V31" s="17">
         <v>2123401</v>
       </c>
-      <c r="W31" s="11">
+      <c r="W31" s="17">
         <v>2123689</v>
       </c>
-      <c r="X31" s="11">
+      <c r="X31" s="29">
         <v>2121405</v>
       </c>
-      <c r="Y31" s="10">
-        <v>-1.964676126971481</v>
-      </c>
-      <c r="Z31" s="10">
-        <v>-1.2396972760976805</v>
-      </c>
-      <c r="AA31" s="10">
-        <v>-0.10766449593547672</v>
-      </c>
-    </row>
-    <row r="32" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="3">
+      <c r="Y31" s="28">
+        <v>-1.964676126971483</v>
+      </c>
+      <c r="Z31" s="28">
+        <v>-1.2245169725436966</v>
+      </c>
+      <c r="AA31" s="28">
+        <v>-0.10754870416525364</v>
+      </c>
+    </row>
+    <row r="32" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="12">
         <v>351</v>
       </c>
-      <c r="C32" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D32" s="9">
+      <c r="C32" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B32</f>
+        <v>Celle</v>
+      </c>
+      <c r="D32" s="14">
         <v>182444</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="14">
         <v>181936</v>
       </c>
-      <c r="F32" s="9">
+      <c r="F32" s="14">
         <v>181115</v>
       </c>
-      <c r="G32" s="9">
+      <c r="G32" s="14">
         <v>180130</v>
       </c>
-      <c r="H32" s="9">
+      <c r="H32" s="14">
         <v>179247</v>
       </c>
-      <c r="I32" s="9">
+      <c r="I32" s="14">
         <v>178528</v>
       </c>
-      <c r="J32" s="9">
+      <c r="J32" s="14">
         <v>176054</v>
       </c>
-      <c r="K32" s="9">
+      <c r="K32" s="14">
         <v>175706</v>
       </c>
-      <c r="L32" s="9">
+      <c r="L32" s="14">
         <v>175552</v>
       </c>
-      <c r="M32" s="9">
+      <c r="M32" s="14">
         <v>176157</v>
       </c>
-      <c r="N32" s="9">
+      <c r="N32" s="14">
         <v>177971</v>
       </c>
-      <c r="O32" s="9">
+      <c r="O32" s="14">
         <v>178370</v>
       </c>
-      <c r="P32" s="9">
+      <c r="P32" s="14">
         <v>178764</v>
       </c>
-      <c r="Q32" s="9">
+      <c r="Q32" s="14">
         <v>178936</v>
       </c>
-      <c r="R32" s="9">
+      <c r="R32" s="14">
         <v>179011</v>
       </c>
-      <c r="S32" s="9">
+      <c r="S32" s="14">
         <v>179386</v>
       </c>
-      <c r="T32" s="9">
+      <c r="T32" s="14">
         <v>179915</v>
       </c>
-      <c r="U32" s="9">
+      <c r="U32" s="14">
         <v>172477</v>
       </c>
-      <c r="V32" s="9">
+      <c r="V32" s="14">
         <v>172871</v>
       </c>
-      <c r="W32" s="11">
+      <c r="W32" s="17">
         <v>172449</v>
       </c>
-      <c r="X32" s="11">
+      <c r="X32" s="29">
         <v>172089</v>
       </c>
-      <c r="Y32" s="10">
-        <v>-5.6757141917519895</v>
-      </c>
-      <c r="Z32" s="10">
-        <v>-4.2402477787656387</v>
-      </c>
-      <c r="AA32" s="10">
-        <v>-0.20919407980754146</v>
-      </c>
-    </row>
-    <row r="33" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="3">
+      <c r="Y32" s="28">
+        <v>-5.6757141917519931</v>
+      </c>
+      <c r="Z32" s="28">
+        <v>-4.0677644855228436</v>
+      </c>
+      <c r="AA32" s="28">
+        <v>-0.20875737174469577</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="12">
         <v>352</v>
       </c>
-      <c r="C33" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D33" s="9">
+      <c r="C33" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B33</f>
+        <v>Cuxhaven</v>
+      </c>
+      <c r="D33" s="14">
         <v>205276</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E33" s="14">
         <v>204235</v>
       </c>
-      <c r="F33" s="9">
+      <c r="F33" s="14">
         <v>202933</v>
       </c>
-      <c r="G33" s="9">
+      <c r="G33" s="14">
         <v>202124</v>
       </c>
-      <c r="H33" s="9">
+      <c r="H33" s="14">
         <v>201188</v>
       </c>
-      <c r="I33" s="9">
+      <c r="I33" s="14">
         <v>200464</v>
       </c>
-      <c r="J33" s="9">
+      <c r="J33" s="14">
         <v>198115</v>
       </c>
-      <c r="K33" s="9">
+      <c r="K33" s="14">
         <v>197433</v>
       </c>
-      <c r="L33" s="9">
+      <c r="L33" s="14">
         <v>196607</v>
       </c>
-      <c r="M33" s="9">
+      <c r="M33" s="14">
         <v>196787</v>
       </c>
-      <c r="N33" s="9">
+      <c r="N33" s="14">
         <v>198103</v>
       </c>
-      <c r="O33" s="9">
+      <c r="O33" s="14">
         <v>198670</v>
       </c>
-      <c r="P33" s="9">
+      <c r="P33" s="14">
         <v>198100</v>
       </c>
-      <c r="Q33" s="9">
+      <c r="Q33" s="14">
         <v>198213</v>
       </c>
-      <c r="R33" s="9">
+      <c r="R33" s="14">
         <v>198038</v>
       </c>
-      <c r="S33" s="9">
+      <c r="S33" s="14">
         <v>198826</v>
       </c>
-      <c r="T33" s="9">
+      <c r="T33" s="14">
         <v>199603</v>
       </c>
-      <c r="U33" s="9">
+      <c r="U33" s="14">
         <v>198898</v>
       </c>
-      <c r="V33" s="9">
+      <c r="V33" s="14">
         <v>199390</v>
       </c>
-      <c r="W33" s="9">
+      <c r="W33" s="14">
         <v>198842</v>
       </c>
-      <c r="X33" s="9">
+      <c r="X33" s="27">
         <v>198886</v>
       </c>
-      <c r="Y33" s="10">
-        <v>-3.1128821683976695</v>
-      </c>
-      <c r="Z33" s="10">
-        <v>3.0168035960298864E-2</v>
-      </c>
-      <c r="AA33" s="10">
-        <v>2.2123226370885835E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="3">
+      <c r="Y33" s="28">
+        <v>-3.1128821683976753</v>
+      </c>
+      <c r="Z33" s="28">
+        <v>3.0177139810689368E-2</v>
+      </c>
+      <c r="AA33" s="28">
+        <v>2.2128121825375047E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="12">
         <v>353</v>
       </c>
-      <c r="C34" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D34" s="9">
+      <c r="C34" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B34</f>
+        <v>Harburg</v>
+      </c>
+      <c r="D34" s="14">
         <v>241827</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E34" s="14">
         <v>242748</v>
       </c>
-      <c r="F34" s="9">
+      <c r="F34" s="14">
         <v>243888</v>
       </c>
-      <c r="G34" s="9">
+      <c r="G34" s="14">
         <v>244640</v>
       </c>
-      <c r="H34" s="9">
+      <c r="H34" s="14">
         <v>245624</v>
       </c>
-      <c r="I34" s="9">
+      <c r="I34" s="14">
         <v>246868</v>
       </c>
-      <c r="J34" s="9">
+      <c r="J34" s="14">
         <v>239269</v>
       </c>
-      <c r="K34" s="9">
+      <c r="K34" s="14">
         <v>240548</v>
       </c>
-      <c r="L34" s="9">
+      <c r="L34" s="14">
         <v>242871</v>
       </c>
-      <c r="M34" s="9">
+      <c r="M34" s="14">
         <v>245199</v>
       </c>
-      <c r="N34" s="9">
+      <c r="N34" s="14">
         <v>248122</v>
       </c>
-      <c r="O34" s="9">
+      <c r="O34" s="14">
         <v>250326</v>
       </c>
-      <c r="P34" s="9">
+      <c r="P34" s="14">
         <v>251511</v>
       </c>
-      <c r="Q34" s="9">
+      <c r="Q34" s="14">
         <v>252776</v>
       </c>
-      <c r="R34" s="9">
+      <c r="R34" s="14">
         <v>254431</v>
       </c>
-      <c r="S34" s="9">
+      <c r="S34" s="14">
         <v>256016</v>
       </c>
-      <c r="T34" s="9">
+      <c r="T34" s="14">
         <v>257548</v>
       </c>
-      <c r="U34" s="9">
+      <c r="U34" s="14">
         <v>262954</v>
       </c>
-      <c r="V34" s="9">
+      <c r="V34" s="14">
         <v>264767</v>
       </c>
-      <c r="W34" s="9">
+      <c r="W34" s="14">
         <v>265864</v>
       </c>
-      <c r="X34" s="9">
+      <c r="X34" s="27">
         <v>265727</v>
       </c>
-      <c r="Y34" s="10">
-        <v>9.8830982479210352</v>
-      </c>
-      <c r="Z34" s="10">
-        <v>3.654502553372446</v>
-      </c>
-      <c r="AA34" s="10">
-        <v>-5.1556672825870162E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="3">
+      <c r="Y34" s="28">
+        <v>9.8830982479210405</v>
+      </c>
+      <c r="Z34" s="28">
+        <v>3.7931223048559417</v>
+      </c>
+      <c r="AA34" s="28">
+        <v>-5.1530105617914046E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="12">
         <v>354</v>
       </c>
-      <c r="C35" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="D35" s="9">
+      <c r="C35" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B35</f>
+        <v>Lüchow-Dannenberg</v>
+      </c>
+      <c r="D35" s="14">
         <v>51352</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E35" s="14">
         <v>50878</v>
       </c>
-      <c r="F35" s="9">
+      <c r="F35" s="14">
         <v>50465</v>
       </c>
-      <c r="G35" s="9">
+      <c r="G35" s="14">
         <v>49965</v>
       </c>
-      <c r="H35" s="9">
+      <c r="H35" s="14">
         <v>49699</v>
       </c>
-      <c r="I35" s="9">
+      <c r="I35" s="14">
         <v>49213</v>
       </c>
-      <c r="J35" s="9">
+      <c r="J35" s="14">
         <v>49082</v>
       </c>
-      <c r="K35" s="9">
+      <c r="K35" s="14">
         <v>48928</v>
       </c>
-      <c r="L35" s="9">
+      <c r="L35" s="14">
         <v>48670</v>
       </c>
-      <c r="M35" s="9">
+      <c r="M35" s="14">
         <v>48728</v>
       </c>
-      <c r="N35" s="9">
+      <c r="N35" s="14">
         <v>50128</v>
       </c>
-      <c r="O35" s="9">
+      <c r="O35" s="14">
         <v>48825</v>
       </c>
-      <c r="P35" s="9">
+      <c r="P35" s="14">
         <v>48357</v>
       </c>
-      <c r="Q35" s="9">
+      <c r="Q35" s="14">
         <v>48424</v>
       </c>
-      <c r="R35" s="9">
+      <c r="R35" s="14">
         <v>48412</v>
       </c>
-      <c r="S35" s="9">
+      <c r="S35" s="14">
         <v>48503</v>
       </c>
-      <c r="T35" s="9">
+      <c r="T35" s="14">
         <v>48472</v>
       </c>
-      <c r="U35" s="9">
+      <c r="U35" s="14">
         <v>46791</v>
       </c>
-      <c r="V35" s="9">
+      <c r="V35" s="14">
         <v>46815</v>
       </c>
-      <c r="W35" s="9">
+      <c r="W35" s="14">
         <v>46502</v>
       </c>
-      <c r="X35" s="9">
+      <c r="X35" s="27">
         <v>46471</v>
       </c>
-      <c r="Y35" s="10">
-        <v>-9.5049852001869457</v>
-      </c>
-      <c r="Z35" s="10">
-        <v>-4.3726194831185037</v>
-      </c>
-      <c r="AA35" s="10">
-        <v>-6.6708269673559861E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="3">
+      <c r="Y35" s="28">
+        <v>-9.504985200186951</v>
+      </c>
+      <c r="Z35" s="28">
+        <v>-4.1894315815516592</v>
+      </c>
+      <c r="AA35" s="28">
+        <v>-6.6663799406470048E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="12">
         <v>355</v>
       </c>
-      <c r="C36" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="D36" s="9">
+      <c r="C36" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B36</f>
+        <v>Lüneburg</v>
+      </c>
+      <c r="D36" s="14">
         <v>175441</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E36" s="14">
         <v>175906</v>
       </c>
-      <c r="F36" s="9">
+      <c r="F36" s="14">
         <v>176445</v>
       </c>
-      <c r="G36" s="9">
+      <c r="G36" s="14">
         <v>176512</v>
       </c>
-      <c r="H36" s="9">
+      <c r="H36" s="14">
         <v>177042</v>
       </c>
-      <c r="I36" s="9">
+      <c r="I36" s="14">
         <v>177279</v>
       </c>
-      <c r="J36" s="9">
+      <c r="J36" s="14">
         <v>174685</v>
       </c>
-      <c r="K36" s="9">
+      <c r="K36" s="14">
         <v>175640</v>
       </c>
-      <c r="L36" s="9">
+      <c r="L36" s="14">
         <v>176727</v>
       </c>
-      <c r="M36" s="9">
+      <c r="M36" s="14">
         <v>178122</v>
       </c>
-      <c r="N36" s="9">
+      <c r="N36" s="14">
         <v>180719</v>
       </c>
-      <c r="O36" s="9">
+      <c r="O36" s="14">
         <v>181605</v>
       </c>
-      <c r="P36" s="9">
+      <c r="P36" s="14">
         <v>182930</v>
       </c>
-      <c r="Q36" s="9">
+      <c r="Q36" s="14">
         <v>183372</v>
       </c>
-      <c r="R36" s="9">
+      <c r="R36" s="14">
         <v>184139</v>
       </c>
-      <c r="S36" s="9">
+      <c r="S36" s="14">
         <v>184235</v>
       </c>
-      <c r="T36" s="9">
+      <c r="T36" s="14">
         <v>185129</v>
       </c>
-      <c r="U36" s="9">
+      <c r="U36" s="14">
         <v>178099</v>
       </c>
-      <c r="V36" s="9">
+      <c r="V36" s="14">
         <v>179403</v>
       </c>
-      <c r="W36" s="9">
+      <c r="W36" s="14">
         <v>179448</v>
       </c>
-      <c r="X36" s="9">
+      <c r="X36" s="27">
         <v>179185</v>
       </c>
-      <c r="Y36" s="10">
-        <v>2.1340507635045398</v>
-      </c>
-      <c r="Z36" s="10">
-        <v>-2.8183162653123865</v>
-      </c>
-      <c r="AA36" s="10">
-        <v>-0.14677567876775399</v>
-      </c>
-    </row>
-    <row r="37" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="3">
+      <c r="Y36" s="28">
+        <v>2.1340507635045469</v>
+      </c>
+      <c r="Z36" s="28">
+        <v>-2.7410644014438077</v>
+      </c>
+      <c r="AA36" s="28">
+        <v>-0.146560563505858</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="12">
         <v>356</v>
       </c>
-      <c r="C37" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D37" s="9">
+      <c r="C37" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B37</f>
+        <v>Osterholz</v>
+      </c>
+      <c r="D37" s="14">
         <v>112741</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E37" s="14">
         <v>112498</v>
       </c>
-      <c r="F37" s="9">
+      <c r="F37" s="14">
         <v>112679</v>
       </c>
-      <c r="G37" s="9">
+      <c r="G37" s="14">
         <v>112486</v>
       </c>
-      <c r="H37" s="9">
+      <c r="H37" s="14">
         <v>112029</v>
       </c>
-      <c r="I37" s="9">
+      <c r="I37" s="14">
         <v>111876</v>
       </c>
-      <c r="J37" s="9">
+      <c r="J37" s="14">
         <v>110842</v>
       </c>
-      <c r="K37" s="9">
+      <c r="K37" s="14">
         <v>110816</v>
       </c>
-      <c r="L37" s="9">
+      <c r="L37" s="14">
         <v>110882</v>
       </c>
-      <c r="M37" s="9">
+      <c r="M37" s="14">
         <v>111484</v>
       </c>
-      <c r="N37" s="9">
+      <c r="N37" s="14">
         <v>113579</v>
       </c>
-      <c r="O37" s="9">
+      <c r="O37" s="14">
         <v>112695</v>
       </c>
-      <c r="P37" s="9">
+      <c r="P37" s="14">
         <v>113105</v>
       </c>
-      <c r="Q37" s="9">
+      <c r="Q37" s="14">
         <v>113517</v>
       </c>
-      <c r="R37" s="9">
+      <c r="R37" s="14">
         <v>113928</v>
       </c>
-      <c r="S37" s="9">
+      <c r="S37" s="14">
         <v>114640</v>
       </c>
-      <c r="T37" s="9">
+      <c r="T37" s="14">
         <v>115054</v>
       </c>
-      <c r="U37" s="9">
+      <c r="U37" s="14">
         <v>113800</v>
       </c>
-      <c r="V37" s="9">
+      <c r="V37" s="14">
         <v>113784</v>
       </c>
-      <c r="W37" s="9">
+      <c r="W37" s="14">
         <v>113598</v>
       </c>
-      <c r="X37" s="9">
+      <c r="X37" s="27">
         <v>113340</v>
       </c>
-      <c r="Y37" s="10">
-        <v>0.53130626834958006</v>
-      </c>
-      <c r="Z37" s="10">
-        <v>-1.1469913534497971</v>
-      </c>
-      <c r="AA37" s="10">
-        <v>-0.22763366860772896</v>
-      </c>
-    </row>
-    <row r="38" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="3">
+      <c r="Y37" s="28">
+        <v>0.5313062683495815</v>
+      </c>
+      <c r="Z37" s="28">
+        <v>-1.1339846475924702</v>
+      </c>
+      <c r="AA37" s="28">
+        <v>-0.2271166745893396</v>
+      </c>
+    </row>
+    <row r="38" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="12">
         <v>357</v>
       </c>
-      <c r="C38" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="D38" s="9">
+      <c r="C38" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B38</f>
+        <v>Rotenburg (Wümme)</v>
+      </c>
+      <c r="D38" s="14">
         <v>164875</v>
       </c>
-      <c r="E38" s="9">
+      <c r="E38" s="14">
         <v>164958</v>
       </c>
-      <c r="F38" s="9">
+      <c r="F38" s="14">
         <v>165074</v>
       </c>
-      <c r="G38" s="9">
+      <c r="G38" s="14">
         <v>164603</v>
       </c>
-      <c r="H38" s="9">
+      <c r="H38" s="14">
         <v>164064</v>
       </c>
-      <c r="I38" s="9">
+      <c r="I38" s="14">
         <v>163860</v>
       </c>
-      <c r="J38" s="9">
+      <c r="J38" s="14">
         <v>162182</v>
       </c>
-      <c r="K38" s="9">
+      <c r="K38" s="14">
         <v>161780</v>
       </c>
-      <c r="L38" s="9">
+      <c r="L38" s="14">
         <v>161308</v>
       </c>
-      <c r="M38" s="9">
+      <c r="M38" s="14">
         <v>161842</v>
       </c>
-      <c r="N38" s="9">
+      <c r="N38" s="14">
         <v>163253</v>
       </c>
-      <c r="O38" s="9">
+      <c r="O38" s="14">
         <v>163372</v>
       </c>
-      <c r="P38" s="9">
+      <c r="P38" s="14">
         <v>163377</v>
       </c>
-      <c r="Q38" s="9">
+      <c r="Q38" s="14">
         <v>163455</v>
       </c>
-      <c r="R38" s="9">
+      <c r="R38" s="14">
         <v>163782</v>
       </c>
-      <c r="S38" s="9">
+      <c r="S38" s="14">
         <v>164486</v>
       </c>
-      <c r="T38" s="9">
+      <c r="T38" s="14">
         <v>165001</v>
       </c>
-      <c r="U38" s="9">
+      <c r="U38" s="14">
         <v>164657</v>
       </c>
-      <c r="V38" s="9">
+      <c r="V38" s="14">
         <v>165561</v>
       </c>
-      <c r="W38" s="9">
+      <c r="W38" s="14">
         <v>165904</v>
       </c>
-      <c r="X38" s="9">
+      <c r="X38" s="27">
         <v>165853</v>
       </c>
-      <c r="Y38" s="10">
-        <v>0.59317664897649736</v>
-      </c>
-      <c r="Z38" s="10">
-        <v>0.82422386088885946</v>
-      </c>
-      <c r="AA38" s="10">
-        <v>-3.0750122096073029E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="3">
+      <c r="Y38" s="28">
+        <v>0.59317664897649536</v>
+      </c>
+      <c r="Z38" s="28">
+        <v>0.83107376919616627</v>
+      </c>
+      <c r="AA38" s="28">
+        <v>-3.0740669302730339E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="12">
         <v>358</v>
       </c>
-      <c r="C39" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="D39" s="9">
+      <c r="C39" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B39</f>
+        <v>Heidekreis</v>
+      </c>
+      <c r="D39" s="14">
         <v>142678</v>
       </c>
-      <c r="E39" s="9">
+      <c r="E39" s="14">
         <v>142234</v>
       </c>
-      <c r="F39" s="9">
+      <c r="F39" s="14">
         <v>141692</v>
       </c>
-      <c r="G39" s="9">
+      <c r="G39" s="14">
         <v>140792</v>
       </c>
-      <c r="H39" s="9">
+      <c r="H39" s="14">
         <v>140053</v>
       </c>
-      <c r="I39" s="9">
+      <c r="I39" s="14">
         <v>139630</v>
       </c>
-      <c r="J39" s="9">
+      <c r="J39" s="14">
         <v>136072</v>
       </c>
-      <c r="K39" s="9">
+      <c r="K39" s="14">
         <v>135772</v>
       </c>
-      <c r="L39" s="9">
+      <c r="L39" s="14">
         <v>136251</v>
       </c>
-      <c r="M39" s="9">
+      <c r="M39" s="14">
         <v>136200</v>
       </c>
-      <c r="N39" s="9">
+      <c r="N39" s="14">
         <v>140264</v>
       </c>
-      <c r="O39" s="9">
+      <c r="O39" s="14">
         <v>139641</v>
       </c>
-      <c r="P39" s="9">
+      <c r="P39" s="14">
         <v>139099</v>
       </c>
-      <c r="Q39" s="9">
+      <c r="Q39" s="14">
         <v>139755</v>
       </c>
-      <c r="R39" s="9">
+      <c r="R39" s="14">
         <v>140673</v>
       </c>
-      <c r="S39" s="9">
+      <c r="S39" s="14">
         <v>140885</v>
       </c>
-      <c r="T39" s="9">
+      <c r="T39" s="14">
         <v>142912</v>
       </c>
-      <c r="U39" s="9">
+      <c r="U39" s="14">
         <v>143728</v>
       </c>
-      <c r="V39" s="9">
+      <c r="V39" s="14">
         <v>141627</v>
       </c>
-      <c r="W39" s="9">
+      <c r="W39" s="14">
         <v>141321</v>
       </c>
-      <c r="X39" s="9">
+      <c r="X39" s="27">
         <v>141473</v>
       </c>
-      <c r="Y39" s="10">
-        <v>-0.84455907708266165</v>
-      </c>
-      <c r="Z39" s="10">
-        <v>0.41562701010086728</v>
-      </c>
-      <c r="AA39" s="10">
-        <v>0.10744099580838747</v>
-      </c>
-    </row>
-    <row r="40" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="3">
+      <c r="Y39" s="28">
+        <v>-0.84455907708266409</v>
+      </c>
+      <c r="Z39" s="28">
+        <v>0.41736167796429413</v>
+      </c>
+      <c r="AA39" s="28">
+        <v>0.10755655564283018</v>
+      </c>
+    </row>
+    <row r="40" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="12">
         <v>359</v>
       </c>
-      <c r="C40" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D40" s="9">
+      <c r="C40" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B40</f>
+        <v>Stade</v>
+      </c>
+      <c r="D40" s="14">
         <v>196475</v>
       </c>
-      <c r="E40" s="9">
+      <c r="E40" s="14">
         <v>197122</v>
       </c>
-      <c r="F40" s="9">
+      <c r="F40" s="14">
         <v>197091</v>
       </c>
-      <c r="G40" s="9">
+      <c r="G40" s="14">
         <v>196891</v>
       </c>
-      <c r="H40" s="9">
+      <c r="H40" s="14">
         <v>196952</v>
       </c>
-      <c r="I40" s="9">
+      <c r="I40" s="14">
         <v>197132</v>
       </c>
-      <c r="J40" s="9">
+      <c r="J40" s="14">
         <v>195606</v>
       </c>
-      <c r="K40" s="9">
+      <c r="K40" s="14">
         <v>195779</v>
       </c>
-      <c r="L40" s="9">
+      <c r="L40" s="14">
         <v>196516</v>
       </c>
-      <c r="M40" s="9">
+      <c r="M40" s="14">
         <v>197448</v>
       </c>
-      <c r="N40" s="9">
+      <c r="N40" s="14">
         <v>200054</v>
       </c>
-      <c r="O40" s="9">
+      <c r="O40" s="14">
         <v>201638</v>
       </c>
-      <c r="P40" s="9">
+      <c r="P40" s="14">
         <v>201887</v>
       </c>
-      <c r="Q40" s="9">
+      <c r="Q40" s="14">
         <v>203102</v>
       </c>
-      <c r="R40" s="9">
+      <c r="R40" s="14">
         <v>204512</v>
       </c>
-      <c r="S40" s="9">
+      <c r="S40" s="14">
         <v>205357</v>
       </c>
-      <c r="T40" s="9">
+      <c r="T40" s="14">
         <v>206496</v>
       </c>
-      <c r="U40" s="9">
+      <c r="U40" s="14">
         <v>206375</v>
       </c>
-      <c r="V40" s="9">
+      <c r="V40" s="14">
         <v>207659</v>
       </c>
-      <c r="W40" s="9">
+      <c r="W40" s="14">
         <v>207700</v>
       </c>
-      <c r="X40" s="9">
+      <c r="X40" s="27">
         <v>207935</v>
       </c>
-      <c r="Y40" s="10">
-        <v>5.8328031556177633</v>
-      </c>
-      <c r="Z40" s="10">
-        <v>1.2398105177098613</v>
-      </c>
-      <c r="AA40" s="10">
-        <v>0.11301608675788107</v>
-      </c>
-    </row>
-    <row r="41" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="3">
+      <c r="Y40" s="28">
+        <v>5.8328031556177677</v>
+      </c>
+      <c r="Z40" s="28">
+        <v>1.255374786347673</v>
+      </c>
+      <c r="AA40" s="28">
+        <v>0.11314395763119478</v>
+      </c>
+    </row>
+    <row r="41" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="12">
         <v>360</v>
       </c>
-      <c r="C41" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D41" s="9">
+      <c r="C41" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B41</f>
+        <v>Uelzen</v>
+      </c>
+      <c r="D41" s="14">
         <v>96940</v>
       </c>
-      <c r="E41" s="9">
+      <c r="E41" s="14">
         <v>96458</v>
       </c>
-      <c r="F41" s="9">
+      <c r="F41" s="14">
         <v>95983</v>
       </c>
-      <c r="G41" s="9">
+      <c r="G41" s="14">
         <v>94940</v>
       </c>
-      <c r="H41" s="9">
+      <c r="H41" s="14">
         <v>94428</v>
       </c>
-      <c r="I41" s="9">
+      <c r="I41" s="14">
         <v>94020</v>
       </c>
-      <c r="J41" s="9">
+      <c r="J41" s="14">
         <v>93284</v>
       </c>
-      <c r="K41" s="9">
+      <c r="K41" s="14">
         <v>92801</v>
       </c>
-      <c r="L41" s="9">
+      <c r="L41" s="14">
         <v>92356</v>
       </c>
-      <c r="M41" s="9">
+      <c r="M41" s="14">
         <v>92533</v>
       </c>
-      <c r="N41" s="9">
+      <c r="N41" s="14">
         <v>93131</v>
       </c>
-      <c r="O41" s="9">
+      <c r="O41" s="14">
         <v>92961</v>
       </c>
-      <c r="P41" s="9">
+      <c r="P41" s="14">
         <v>92744</v>
       </c>
-      <c r="Q41" s="9">
+      <c r="Q41" s="14">
         <v>92572</v>
       </c>
-      <c r="R41" s="9">
+      <c r="R41" s="14">
         <v>92389</v>
       </c>
-      <c r="S41" s="9">
+      <c r="S41" s="14">
         <v>92566</v>
       </c>
-      <c r="T41" s="9">
+      <c r="T41" s="14">
         <v>92894</v>
       </c>
-      <c r="U41" s="9">
+      <c r="U41" s="14">
         <v>91059</v>
       </c>
-      <c r="V41" s="9">
+      <c r="V41" s="14">
         <v>91832</v>
       </c>
-      <c r="W41" s="9">
+      <c r="W41" s="14">
         <v>91638</v>
       </c>
-      <c r="X41" s="9">
+      <c r="X41" s="27">
         <v>91367</v>
       </c>
-      <c r="Y41" s="10">
-        <v>-5.7489168557870851</v>
-      </c>
-      <c r="Z41" s="10">
-        <v>-1.3122899952937057</v>
-      </c>
-      <c r="AA41" s="10">
-        <v>-0.29660599560016199</v>
-      </c>
-    </row>
-    <row r="42" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="3">
+      <c r="Y41" s="28">
+        <v>-5.7489168557870869</v>
+      </c>
+      <c r="Z41" s="28">
+        <v>-1.2952920078646599</v>
+      </c>
+      <c r="AA41" s="28">
+        <v>-0.29572884611187078</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="12">
         <v>361</v>
       </c>
-      <c r="C42" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D42" s="9">
+      <c r="C42" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B42</f>
+        <v>Verden</v>
+      </c>
+      <c r="D42" s="14">
         <v>134084</v>
       </c>
-      <c r="E42" s="9">
+      <c r="E42" s="14">
         <v>133965</v>
       </c>
-      <c r="F42" s="9">
+      <c r="F42" s="14">
         <v>133767</v>
       </c>
-      <c r="G42" s="9">
+      <c r="G42" s="14">
         <v>133560</v>
       </c>
-      <c r="H42" s="9">
+      <c r="H42" s="14">
         <v>133328</v>
       </c>
-      <c r="I42" s="9">
+      <c r="I42" s="14">
         <v>133368</v>
       </c>
-      <c r="J42" s="9">
+      <c r="J42" s="14">
         <v>131936</v>
       </c>
-      <c r="K42" s="9">
+      <c r="K42" s="14">
         <v>132129</v>
       </c>
-      <c r="L42" s="9">
+      <c r="L42" s="14">
         <v>132459</v>
       </c>
-      <c r="M42" s="9">
+      <c r="M42" s="14">
         <v>133215</v>
       </c>
-      <c r="N42" s="9">
+      <c r="N42" s="14">
         <v>134645</v>
       </c>
-      <c r="O42" s="9">
+      <c r="O42" s="14">
         <v>135842</v>
       </c>
-      <c r="P42" s="9">
+      <c r="P42" s="14">
         <v>136590</v>
       </c>
-      <c r="Q42" s="9">
+      <c r="Q42" s="14">
         <v>136792</v>
       </c>
-      <c r="R42" s="9">
+      <c r="R42" s="14">
         <v>137133</v>
       </c>
-      <c r="S42" s="9">
+      <c r="S42" s="14">
         <v>137574</v>
       </c>
-      <c r="T42" s="9">
+      <c r="T42" s="14">
         <v>138507</v>
       </c>
-      <c r="U42" s="9">
+      <c r="U42" s="14">
         <v>137793</v>
       </c>
-      <c r="V42" s="9">
+      <c r="V42" s="14">
         <v>138273</v>
       </c>
-      <c r="W42" s="9">
+      <c r="W42" s="14">
         <v>138626</v>
       </c>
-      <c r="X42" s="9">
+      <c r="X42" s="27">
         <v>138895</v>
       </c>
-      <c r="Y42" s="10">
-        <v>3.5880492825393038</v>
-      </c>
-      <c r="Z42" s="10">
-        <v>0.95107815256128725</v>
-      </c>
-      <c r="AA42" s="10">
-        <v>0.19367147845494798</v>
-      </c>
-    </row>
-    <row r="43" spans="2:27" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="5">
+      <c r="Y42" s="28">
+        <v>3.588049282539302</v>
+      </c>
+      <c r="Z42" s="28">
+        <v>0.9602105048919185</v>
+      </c>
+      <c r="AA42" s="28">
+        <v>0.19404729271565202</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="15">
         <v>3</v>
       </c>
-      <c r="C43" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="D43" s="11">
+      <c r="C43" s="16" t="str">
+        <f>[1]A1_2021_Berechnung!B43</f>
+        <v>Statistische Region Lüneburg</v>
+      </c>
+      <c r="D43" s="17">
         <v>1704133</v>
       </c>
-      <c r="E43" s="11">
+      <c r="E43" s="17">
         <v>1702938</v>
       </c>
-      <c r="F43" s="11">
+      <c r="F43" s="17">
         <v>1701132</v>
       </c>
-      <c r="G43" s="11">
+      <c r="G43" s="17">
         <v>1696643</v>
       </c>
-      <c r="H43" s="11">
+      <c r="H43" s="17">
         <v>1693654</v>
       </c>
-      <c r="I43" s="11">
+      <c r="I43" s="17">
         <v>1692238</v>
       </c>
-      <c r="J43" s="11">
+      <c r="J43" s="17">
         <v>1667127</v>
       </c>
-      <c r="K43" s="11">
+      <c r="K43" s="17">
         <v>1667332</v>
       </c>
-      <c r="L43" s="11">
+      <c r="L43" s="17">
         <v>1670199</v>
       </c>
-      <c r="M43" s="11">
+      <c r="M43" s="17">
         <v>1677715</v>
       </c>
-      <c r="N43" s="11">
+      <c r="N43" s="17">
         <v>1699969</v>
       </c>
-      <c r="O43" s="11">
+      <c r="O43" s="17">
         <v>1703945</v>
       </c>
-      <c r="P43" s="11">
+      <c r="P43" s="17">
         <v>1706464</v>
       </c>
-      <c r="Q43" s="11">
+      <c r="Q43" s="17">
         <v>1710914</v>
       </c>
-      <c r="R43" s="11">
+      <c r="R43" s="17">
         <v>1716448</v>
       </c>
-      <c r="S43" s="11">
+      <c r="S43" s="17">
         <v>1722474</v>
       </c>
-      <c r="T43" s="11">
+      <c r="T43" s="17">
         <v>1731531</v>
       </c>
-      <c r="U43" s="11">
+      <c r="U43" s="17">
         <v>1716631</v>
       </c>
-      <c r="V43" s="11">
+      <c r="V43" s="17">
         <v>1721982</v>
       </c>
-      <c r="W43" s="11">
+      <c r="W43" s="17">
         <v>1721892</v>
       </c>
-      <c r="X43" s="11">
+      <c r="X43" s="29">
         <v>1721221</v>
       </c>
-      <c r="Y43" s="10">
-        <v>1.0027386360102175</v>
-      </c>
-      <c r="Z43" s="10">
-        <v>-7.2797159690707935E-2</v>
-      </c>
-      <c r="AA43" s="10">
-        <v>-3.8983953832773366E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="3">
+      <c r="Y43" s="28">
+        <v>1.0027386360102213</v>
+      </c>
+      <c r="Z43" s="28">
+        <v>-7.2744203976370159E-2</v>
+      </c>
+      <c r="AA43" s="28">
+        <v>-3.8968762268481782E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="12">
         <v>401</v>
       </c>
-      <c r="C44" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="D44" s="9">
+      <c r="C44" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B44</f>
+        <v>Delmenhorst, Stadt</v>
+      </c>
+      <c r="D44" s="14">
         <v>75916</v>
       </c>
-      <c r="E44" s="9">
+      <c r="E44" s="14">
         <v>75320</v>
       </c>
-      <c r="F44" s="9">
+      <c r="F44" s="14">
         <v>75135</v>
       </c>
-      <c r="G44" s="9">
+      <c r="G44" s="14">
         <v>74751</v>
       </c>
-      <c r="H44" s="9">
+      <c r="H44" s="14">
         <v>74512</v>
       </c>
-      <c r="I44" s="9">
+      <c r="I44" s="14">
         <v>74361</v>
       </c>
-      <c r="J44" s="9">
+      <c r="J44" s="14">
         <v>73364</v>
       </c>
-      <c r="K44" s="9">
+      <c r="K44" s="14">
         <v>73588</v>
       </c>
-      <c r="L44" s="9">
+      <c r="L44" s="14">
         <v>74052</v>
       </c>
-      <c r="M44" s="9">
+      <c r="M44" s="14">
         <v>74804</v>
       </c>
-      <c r="N44" s="9">
+      <c r="N44" s="14">
         <v>76323</v>
       </c>
-      <c r="O44" s="9">
+      <c r="O44" s="14">
         <v>77045</v>
       </c>
-      <c r="P44" s="9">
+      <c r="P44" s="14">
         <v>77521</v>
       </c>
-      <c r="Q44" s="9">
+      <c r="Q44" s="14">
         <v>77607</v>
       </c>
-      <c r="R44" s="9">
+      <c r="R44" s="14">
         <v>77559</v>
       </c>
-      <c r="S44" s="9">
+      <c r="S44" s="14">
         <v>77503</v>
       </c>
-      <c r="T44" s="9">
+      <c r="T44" s="14">
         <v>77522</v>
       </c>
-      <c r="U44" s="9">
+      <c r="U44" s="14">
         <v>81148</v>
       </c>
-      <c r="V44" s="9">
+      <c r="V44" s="14">
         <v>81746</v>
       </c>
-      <c r="W44" s="9">
+      <c r="W44" s="14">
         <v>81406</v>
       </c>
-      <c r="X44" s="9">
+      <c r="X44" s="27">
         <v>81274</v>
       </c>
-      <c r="Y44" s="10">
-        <v>7.0578007271194476</v>
-      </c>
-      <c r="Z44" s="10">
-        <v>4.6398602259025026</v>
-      </c>
-      <c r="AA44" s="10">
-        <v>-0.16241356399340504</v>
-      </c>
-    </row>
-    <row r="45" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="3">
+      <c r="Y44" s="28">
+        <v>7.0578007271194423</v>
+      </c>
+      <c r="Z44" s="28">
+        <v>4.8656181051056109</v>
+      </c>
+      <c r="AA44" s="28">
+        <v>-0.16215021005822905</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="12">
         <v>402</v>
       </c>
-      <c r="C45" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D45" s="9">
+      <c r="C45" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B45</f>
+        <v>Emden, Stadt</v>
+      </c>
+      <c r="D45" s="14">
         <v>51693</v>
       </c>
-      <c r="E45" s="9">
+      <c r="E45" s="14">
         <v>51742</v>
       </c>
-      <c r="F45" s="9">
+      <c r="F45" s="14">
         <v>51714</v>
       </c>
-      <c r="G45" s="9">
+      <c r="G45" s="14">
         <v>51562</v>
       </c>
-      <c r="H45" s="9">
+      <c r="H45" s="14">
         <v>51292</v>
       </c>
-      <c r="I45" s="9">
+      <c r="I45" s="14">
         <v>51616</v>
       </c>
-      <c r="J45" s="9">
+      <c r="J45" s="14">
         <v>49848</v>
       </c>
-      <c r="K45" s="9">
+      <c r="K45" s="14">
         <v>49751</v>
       </c>
-      <c r="L45" s="9">
+      <c r="L45" s="14">
         <v>49790</v>
       </c>
-      <c r="M45" s="9">
+      <c r="M45" s="14">
         <v>50016</v>
       </c>
-      <c r="N45" s="9">
+      <c r="N45" s="14">
         <v>50694</v>
       </c>
-      <c r="O45" s="9">
+      <c r="O45" s="14">
         <v>50486</v>
       </c>
-      <c r="P45" s="9">
+      <c r="P45" s="14">
         <v>50607</v>
       </c>
-      <c r="Q45" s="9">
+      <c r="Q45" s="14">
         <v>50195</v>
       </c>
-      <c r="R45" s="9">
+      <c r="R45" s="14">
         <v>49913</v>
       </c>
-      <c r="S45" s="9">
+      <c r="S45" s="14">
         <v>49874</v>
       </c>
-      <c r="T45" s="9">
+      <c r="T45" s="14">
         <v>49523</v>
       </c>
-      <c r="U45" s="9">
+      <c r="U45" s="14">
         <v>49563</v>
       </c>
-      <c r="V45" s="9">
+      <c r="V45" s="14">
         <v>49701</v>
       </c>
-      <c r="W45" s="9">
+      <c r="W45" s="14">
         <v>49202</v>
       </c>
-      <c r="X45" s="9">
+      <c r="X45" s="27">
         <v>49009</v>
       </c>
-      <c r="Y45" s="10">
-        <v>-5.1921923664712821</v>
-      </c>
-      <c r="Z45" s="10">
-        <v>-1.7649819420922688</v>
-      </c>
-      <c r="AA45" s="10">
-        <v>-0.39380521944948887</v>
-      </c>
-    </row>
-    <row r="46" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="3">
+      <c r="Y45" s="28">
+        <v>-5.1921923664712892</v>
+      </c>
+      <c r="Z45" s="28">
+        <v>-1.7343706139471493</v>
+      </c>
+      <c r="AA45" s="28">
+        <v>-0.39226047721636803</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="12">
         <v>403</v>
       </c>
-      <c r="C46" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D46" s="9">
+      <c r="C46" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B46</f>
+        <v>Oldenburg (Oldb), Stadt</v>
+      </c>
+      <c r="D46" s="14">
         <v>158565</v>
       </c>
-      <c r="E46" s="9">
+      <c r="E46" s="14">
         <v>159060</v>
       </c>
-      <c r="F46" s="9">
+      <c r="F46" s="14">
         <v>159563</v>
       </c>
-      <c r="G46" s="9">
+      <c r="G46" s="14">
         <v>160279</v>
       </c>
-      <c r="H46" s="9">
+      <c r="H46" s="14">
         <v>161334</v>
       </c>
-      <c r="I46" s="9">
+      <c r="I46" s="14">
         <v>162173</v>
       </c>
-      <c r="J46" s="9">
+      <c r="J46" s="14">
         <v>157706</v>
       </c>
-      <c r="K46" s="9">
+      <c r="K46" s="14">
         <v>158658</v>
       </c>
-      <c r="L46" s="9">
+      <c r="L46" s="14">
         <v>159610</v>
       </c>
-      <c r="M46" s="9">
+      <c r="M46" s="14">
         <v>160907</v>
       </c>
-      <c r="N46" s="9">
+      <c r="N46" s="14">
         <v>163830</v>
       </c>
-      <c r="O46" s="9">
+      <c r="O46" s="14">
         <v>165711</v>
       </c>
-      <c r="P46" s="9">
+      <c r="P46" s="14">
         <v>167081</v>
       </c>
-      <c r="Q46" s="9">
+      <c r="Q46" s="14">
         <v>168210</v>
       </c>
-      <c r="R46" s="9">
+      <c r="R46" s="14">
         <v>169077</v>
       </c>
-      <c r="S46" s="9">
+      <c r="S46" s="14">
         <v>169605</v>
       </c>
-      <c r="T46" s="9">
+      <c r="T46" s="14">
         <v>170389</v>
       </c>
-      <c r="U46" s="9">
+      <c r="U46" s="14">
         <v>174445</v>
       </c>
-      <c r="V46" s="9">
+      <c r="V46" s="14">
         <v>176242</v>
       </c>
-      <c r="W46" s="9">
+      <c r="W46" s="14">
         <v>176614</v>
       </c>
-      <c r="X46" s="9">
+      <c r="X46" s="27">
         <v>177055</v>
       </c>
-      <c r="Y46" s="10">
-        <v>11.660833096837258</v>
-      </c>
-      <c r="Z46" s="10">
-        <v>4.2077320606591169</v>
-      </c>
-      <c r="AA46" s="10">
-        <v>0.24907514614102963</v>
-      </c>
-    </row>
-    <row r="47" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="3">
+      <c r="Y46" s="28">
+        <v>11.660833096837266</v>
+      </c>
+      <c r="Z46" s="28">
+        <v>4.3925591816279024</v>
+      </c>
+      <c r="AA46" s="28">
+        <v>0.24969707950671705</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="12">
         <v>404</v>
       </c>
-      <c r="C47" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D47" s="9">
+      <c r="C47" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B47</f>
+        <v>Osnabrück, Stadt</v>
+      </c>
+      <c r="D47" s="14">
         <v>163814</v>
       </c>
-      <c r="E47" s="9">
+      <c r="E47" s="14">
         <v>163020</v>
       </c>
-      <c r="F47" s="9">
+      <c r="F47" s="14">
         <v>162870</v>
       </c>
-      <c r="G47" s="9">
+      <c r="G47" s="14">
         <v>163286</v>
       </c>
-      <c r="H47" s="9">
+      <c r="H47" s="14">
         <v>163514</v>
       </c>
-      <c r="I47" s="9">
+      <c r="I47" s="14">
         <v>164119</v>
       </c>
-      <c r="J47" s="9">
+      <c r="J47" s="14">
         <v>154513</v>
       </c>
-      <c r="K47" s="9">
+      <c r="K47" s="14">
         <v>155625</v>
       </c>
-      <c r="L47" s="9">
+      <c r="L47" s="14">
         <v>156315</v>
       </c>
-      <c r="M47" s="9">
+      <c r="M47" s="14">
         <v>156897</v>
       </c>
-      <c r="N47" s="9">
+      <c r="N47" s="14">
         <v>162403</v>
       </c>
-      <c r="O47" s="9">
+      <c r="O47" s="14">
         <v>164070</v>
       </c>
-      <c r="P47" s="9">
+      <c r="P47" s="14">
         <v>164374</v>
       </c>
-      <c r="Q47" s="9">
+      <c r="Q47" s="14">
         <v>164748</v>
       </c>
-      <c r="R47" s="9">
+      <c r="R47" s="14">
         <v>165251</v>
       </c>
-      <c r="S47" s="9">
+      <c r="S47" s="14">
         <v>164223</v>
       </c>
-      <c r="T47" s="9">
+      <c r="T47" s="14">
         <v>165034</v>
       </c>
-      <c r="U47" s="9">
+      <c r="U47" s="14">
         <v>165741</v>
       </c>
-      <c r="V47" s="9">
+      <c r="V47" s="14">
         <v>165686</v>
       </c>
-      <c r="W47" s="9">
+      <c r="W47" s="14">
         <v>166057</v>
       </c>
-      <c r="X47" s="9">
+      <c r="X47" s="27">
         <v>166257</v>
       </c>
-      <c r="Y47" s="10">
-        <v>1.4913255277326725</v>
-      </c>
-      <c r="Z47" s="10">
-        <v>1.223407134737184</v>
-      </c>
-      <c r="AA47" s="10">
-        <v>0.12029568679814985</v>
-      </c>
-    </row>
-    <row r="48" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="3">
+      <c r="Y47" s="28">
+        <v>1.4913255277326698</v>
+      </c>
+      <c r="Z47" s="28">
+        <v>1.2385597632487588</v>
+      </c>
+      <c r="AA47" s="28">
+        <v>0.12044057161095623</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="12">
         <v>405</v>
       </c>
-      <c r="C48" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D48" s="9">
+      <c r="C48" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B48</f>
+        <v>Wilhelmshaven, Stadt</v>
+      </c>
+      <c r="D48" s="14">
         <v>83552</v>
       </c>
-      <c r="E48" s="9">
+      <c r="E48" s="14">
         <v>82797</v>
       </c>
-      <c r="F48" s="9">
+      <c r="F48" s="14">
         <v>82192</v>
       </c>
-      <c r="G48" s="9">
+      <c r="G48" s="14">
         <v>81411</v>
       </c>
-      <c r="H48" s="9">
+      <c r="H48" s="14">
         <v>81137</v>
       </c>
-      <c r="I48" s="9">
+      <c r="I48" s="14">
         <v>81324</v>
       </c>
-      <c r="J48" s="9">
+      <c r="J48" s="14">
         <v>76926</v>
       </c>
-      <c r="K48" s="9">
+      <c r="K48" s="14">
         <v>76545</v>
       </c>
-      <c r="L48" s="9">
+      <c r="L48" s="14">
         <v>75728</v>
       </c>
-      <c r="M48" s="9">
+      <c r="M48" s="14">
         <v>75534</v>
       </c>
-      <c r="N48" s="9">
+      <c r="N48" s="14">
         <v>75995</v>
       </c>
-      <c r="O48" s="9">
+      <c r="O48" s="14">
         <v>76201</v>
       </c>
-      <c r="P48" s="9">
+      <c r="P48" s="14">
         <v>76316</v>
       </c>
-      <c r="Q48" s="9">
+      <c r="Q48" s="14">
         <v>76278</v>
       </c>
-      <c r="R48" s="9">
+      <c r="R48" s="14">
         <v>76089</v>
       </c>
-      <c r="S48" s="9">
+      <c r="S48" s="14">
         <v>75189</v>
       </c>
-      <c r="T48" s="9">
+      <c r="T48" s="14">
         <v>75027</v>
       </c>
-      <c r="U48" s="9">
+      <c r="U48" s="14">
         <v>75860</v>
       </c>
-      <c r="V48" s="9">
+      <c r="V48" s="14">
         <v>76010</v>
       </c>
-      <c r="W48" s="9">
+      <c r="W48" s="14">
         <v>75745</v>
       </c>
-      <c r="X48" s="9">
+      <c r="X48" s="27">
         <v>75324</v>
       </c>
-      <c r="Y48" s="10">
-        <v>-9.847759479126772</v>
-      </c>
-      <c r="Z48" s="10">
-        <v>0.17922574478253944</v>
-      </c>
-      <c r="AA48" s="10">
-        <v>-0.55891880409962291</v>
-      </c>
-    </row>
-    <row r="49" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="3">
+      <c r="Y48" s="28">
+        <v>-9.8477594791267649</v>
+      </c>
+      <c r="Z48" s="28">
+        <v>0.17954754019869767</v>
+      </c>
+      <c r="AA48" s="28">
+        <v>-0.55581226483596424</v>
+      </c>
+    </row>
+    <row r="49" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="12">
         <v>451</v>
       </c>
-      <c r="C49" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="D49" s="9">
+      <c r="C49" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B49</f>
+        <v>Ammerland</v>
+      </c>
+      <c r="D49" s="14">
         <v>115891</v>
       </c>
-      <c r="E49" s="9">
+      <c r="E49" s="14">
         <v>116626</v>
       </c>
-      <c r="F49" s="9">
+      <c r="F49" s="14">
         <v>117041</v>
       </c>
-      <c r="G49" s="9">
+      <c r="G49" s="14">
         <v>117102</v>
       </c>
-      <c r="H49" s="9">
+      <c r="H49" s="14">
         <v>117517</v>
       </c>
-      <c r="I49" s="9">
+      <c r="I49" s="14">
         <v>118004</v>
       </c>
-      <c r="J49" s="9">
+      <c r="J49" s="14">
         <v>117951</v>
       </c>
-      <c r="K49" s="9">
+      <c r="K49" s="14">
         <v>118489</v>
       </c>
-      <c r="L49" s="9">
+      <c r="L49" s="14">
         <v>118865</v>
       </c>
-      <c r="M49" s="9">
+      <c r="M49" s="14">
         <v>119917</v>
       </c>
-      <c r="N49" s="9">
+      <c r="N49" s="14">
         <v>121435</v>
       </c>
-      <c r="O49" s="9">
+      <c r="O49" s="14">
         <v>122698</v>
       </c>
-      <c r="P49" s="9">
+      <c r="P49" s="14">
         <v>123377</v>
       </c>
-      <c r="Q49" s="9">
+      <c r="Q49" s="14">
         <v>124071</v>
       </c>
-      <c r="R49" s="9">
+      <c r="R49" s="14">
         <v>124859</v>
       </c>
-      <c r="S49" s="9">
+      <c r="S49" s="14">
         <v>125643</v>
       </c>
-      <c r="T49" s="9">
+      <c r="T49" s="14">
         <v>126475</v>
       </c>
-      <c r="U49" s="9">
+      <c r="U49" s="14">
         <v>126390</v>
       </c>
-      <c r="V49" s="9">
+      <c r="V49" s="14">
         <v>127292</v>
       </c>
-      <c r="W49" s="9">
+      <c r="W49" s="14">
         <v>127751</v>
       </c>
-      <c r="X49" s="9">
+      <c r="X49" s="27">
         <v>127632</v>
       </c>
-      <c r="Y49" s="10">
-        <v>10.131071437816569</v>
-      </c>
-      <c r="Z49" s="10">
-        <v>1.5583866115080858</v>
-      </c>
-      <c r="AA49" s="10">
-        <v>-9.3236805816723084E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="3">
+      <c r="Y49" s="28">
+        <v>10.131071437816573</v>
+      </c>
+      <c r="Z49" s="28">
+        <v>1.5830567560469007</v>
+      </c>
+      <c r="AA49" s="28">
+        <v>-9.314995577334173E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="12">
         <v>452</v>
       </c>
-      <c r="C50" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D50" s="9">
+      <c r="C50" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B50</f>
+        <v>Aurich</v>
+      </c>
+      <c r="D50" s="14">
         <v>190128</v>
       </c>
-      <c r="E50" s="9">
+      <c r="E50" s="14">
         <v>190252</v>
       </c>
-      <c r="F50" s="9">
+      <c r="F50" s="14">
         <v>190293</v>
       </c>
-      <c r="G50" s="9">
+      <c r="G50" s="14">
         <v>189381</v>
       </c>
-      <c r="H50" s="9">
+      <c r="H50" s="14">
         <v>188973</v>
       </c>
-      <c r="I50" s="9">
+      <c r="I50" s="14">
         <v>188947</v>
       </c>
-      <c r="J50" s="9">
+      <c r="J50" s="14">
         <v>186713</v>
       </c>
-      <c r="K50" s="9">
+      <c r="K50" s="14">
         <v>186673</v>
       </c>
-      <c r="L50" s="9">
+      <c r="L50" s="14">
         <v>187058</v>
       </c>
-      <c r="M50" s="9">
+      <c r="M50" s="14">
         <v>187998</v>
       </c>
-      <c r="N50" s="9">
+      <c r="N50" s="14">
         <v>189199</v>
       </c>
-      <c r="O50" s="9">
+      <c r="O50" s="14">
         <v>190066</v>
       </c>
-      <c r="P50" s="9">
+      <c r="P50" s="14">
         <v>189949</v>
       </c>
-      <c r="Q50" s="9">
+      <c r="Q50" s="14">
         <v>189848</v>
       </c>
-      <c r="R50" s="9">
+      <c r="R50" s="14">
         <v>189694</v>
       </c>
-      <c r="S50" s="9">
+      <c r="S50" s="14">
         <v>190178</v>
       </c>
-      <c r="T50" s="9">
+      <c r="T50" s="14">
         <v>190425</v>
       </c>
-      <c r="U50" s="9">
+      <c r="U50" s="14">
         <v>188402</v>
       </c>
-      <c r="V50" s="9">
+      <c r="V50" s="14">
         <v>188960</v>
       </c>
-      <c r="W50" s="9">
+      <c r="W50" s="14">
         <v>188816</v>
       </c>
-      <c r="X50" s="9">
+      <c r="X50" s="27">
         <v>188450</v>
       </c>
-      <c r="Y50" s="10">
-        <v>-0.88256332575948837</v>
-      </c>
-      <c r="Z50" s="10">
-        <v>-0.91695409923056515</v>
-      </c>
-      <c r="AA50" s="10">
-        <v>-0.19421597240647387</v>
-      </c>
-    </row>
-    <row r="51" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="3">
+      <c r="Y50" s="28">
+        <v>-0.88256332575949159</v>
+      </c>
+      <c r="Z50" s="28">
+        <v>-0.9086224484430403</v>
+      </c>
+      <c r="AA50" s="28">
+        <v>-0.19383950512668946</v>
+      </c>
+    </row>
+    <row r="51" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="12">
         <v>453</v>
       </c>
-      <c r="C51" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D51" s="9">
+      <c r="C51" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B51</f>
+        <v>Cloppenburg</v>
+      </c>
+      <c r="D51" s="14">
         <v>155642</v>
       </c>
-      <c r="E51" s="9">
+      <c r="E51" s="14">
         <v>156241</v>
       </c>
-      <c r="F51" s="9">
+      <c r="F51" s="14">
         <v>157164</v>
       </c>
-      <c r="G51" s="9">
+      <c r="G51" s="14">
         <v>157268</v>
       </c>
-      <c r="H51" s="9">
+      <c r="H51" s="14">
         <v>157506</v>
       </c>
-      <c r="I51" s="9">
+      <c r="I51" s="14">
         <v>158194</v>
       </c>
-      <c r="J51" s="9">
+      <c r="J51" s="14">
         <v>159290</v>
       </c>
-      <c r="K51" s="9">
+      <c r="K51" s="14">
         <v>160033</v>
       </c>
-      <c r="L51" s="9">
+      <c r="L51" s="14">
         <v>160176</v>
       </c>
-      <c r="M51" s="9">
+      <c r="M51" s="14">
         <v>162350</v>
       </c>
-      <c r="N51" s="9">
+      <c r="N51" s="14">
         <v>164734</v>
       </c>
-      <c r="O51" s="9">
+      <c r="O51" s="14">
         <v>165930</v>
       </c>
-      <c r="P51" s="9">
+      <c r="P51" s="14">
         <v>167925</v>
       </c>
-      <c r="Q51" s="9">
+      <c r="Q51" s="14">
         <v>169348</v>
       </c>
-      <c r="R51" s="9">
+      <c r="R51" s="14">
         <v>170682</v>
       </c>
-      <c r="S51" s="9">
+      <c r="S51" s="14">
         <v>172632</v>
       </c>
-      <c r="T51" s="9">
+      <c r="T51" s="14">
         <v>173980</v>
       </c>
-      <c r="U51" s="9">
+      <c r="U51" s="14">
         <v>175549</v>
       </c>
-      <c r="V51" s="9">
+      <c r="V51" s="14">
         <v>176540</v>
       </c>
-      <c r="W51" s="9">
+      <c r="W51" s="14">
         <v>177025</v>
       </c>
-      <c r="X51" s="9">
+      <c r="X51" s="27">
         <v>177849</v>
       </c>
-      <c r="Y51" s="10">
+      <c r="Y51" s="28">
         <v>14.267999640199946</v>
       </c>
-      <c r="Z51" s="10">
-        <v>2.933387311708247</v>
-      </c>
-      <c r="AA51" s="10">
-        <v>0.4633143846746397</v>
-      </c>
-    </row>
-    <row r="52" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="3">
+      <c r="Z51" s="28">
+        <v>3.0220353121089971</v>
+      </c>
+      <c r="AA51" s="28">
+        <v>0.46547097867532727</v>
+      </c>
+    </row>
+    <row r="52" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="12">
         <v>454</v>
       </c>
-      <c r="C52" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="D52" s="9">
+      <c r="C52" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B52</f>
+        <v>Emsland</v>
+      </c>
+      <c r="D52" s="14">
         <v>310088</v>
       </c>
-      <c r="E52" s="9">
+      <c r="E52" s="14">
         <v>311965</v>
       </c>
-      <c r="F52" s="9">
+      <c r="F52" s="14">
         <v>313533</v>
       </c>
-      <c r="G52" s="9">
+      <c r="G52" s="14">
         <v>313824</v>
       </c>
-      <c r="H52" s="9">
+      <c r="H52" s="14">
         <v>313098</v>
       </c>
-      <c r="I52" s="9">
+      <c r="I52" s="14">
         <v>313056</v>
       </c>
-      <c r="J52" s="9">
+      <c r="J52" s="14">
         <v>311634</v>
       </c>
-      <c r="K52" s="9">
+      <c r="K52" s="14">
         <v>312855</v>
       </c>
-      <c r="L52" s="9">
+      <c r="L52" s="14">
         <v>313689</v>
       </c>
-      <c r="M52" s="9">
+      <c r="M52" s="14">
         <v>315757</v>
       </c>
-      <c r="N52" s="9">
+      <c r="N52" s="14">
         <v>319488</v>
       </c>
-      <c r="O52" s="9">
+      <c r="O52" s="14">
         <v>321391</v>
       </c>
-      <c r="P52" s="9">
+      <c r="P52" s="14">
         <v>323636</v>
       </c>
-      <c r="Q52" s="9">
+      <c r="Q52" s="14">
         <v>325657</v>
       </c>
-      <c r="R52" s="9">
+      <c r="R52" s="14">
         <v>326954</v>
       </c>
-      <c r="S52" s="9">
+      <c r="S52" s="14">
         <v>328930</v>
       </c>
-      <c r="T52" s="9">
+      <c r="T52" s="14">
         <v>331397</v>
       </c>
-      <c r="U52" s="9">
+      <c r="U52" s="14">
         <v>331711</v>
       </c>
-      <c r="V52" s="9">
+      <c r="V52" s="14">
         <v>334203</v>
       </c>
-      <c r="W52" s="9">
+      <c r="W52" s="14">
         <v>334539</v>
       </c>
-      <c r="X52" s="9">
+      <c r="X52" s="27">
         <v>334403</v>
       </c>
-      <c r="Y52" s="10">
-        <v>7.8413224633007408</v>
-      </c>
-      <c r="Z52" s="10">
-        <v>1.636647996578978</v>
-      </c>
-      <c r="AA52" s="10">
-        <v>-4.0669491601450947E-2</v>
-      </c>
-    </row>
-    <row r="53" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="3">
+      <c r="Y52" s="28">
+        <v>7.8413224633007417</v>
+      </c>
+      <c r="Z52" s="28">
+        <v>1.6638798528562262</v>
+      </c>
+      <c r="AA52" s="28">
+        <v>-4.0652958250007032E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="12">
         <v>455</v>
       </c>
-      <c r="C53" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="D53" s="9">
+      <c r="C53" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B53</f>
+        <v>Friesland</v>
+      </c>
+      <c r="D53" s="14">
         <v>101412</v>
       </c>
-      <c r="E53" s="9">
+      <c r="E53" s="14">
         <v>101192</v>
       </c>
-      <c r="F53" s="9">
+      <c r="F53" s="14">
         <v>100779</v>
       </c>
-      <c r="G53" s="9">
+      <c r="G53" s="14">
         <v>100307</v>
       </c>
-      <c r="H53" s="9">
+      <c r="H53" s="14">
         <v>99851</v>
       </c>
-      <c r="I53" s="9">
+      <c r="I53" s="14">
         <v>99598</v>
       </c>
-      <c r="J53" s="9">
+      <c r="J53" s="14">
         <v>97857</v>
       </c>
-      <c r="K53" s="9">
+      <c r="K53" s="14">
         <v>97327</v>
       </c>
-      <c r="L53" s="9">
+      <c r="L53" s="14">
         <v>97093</v>
       </c>
-      <c r="M53" s="9">
+      <c r="M53" s="14">
         <v>96937</v>
       </c>
-      <c r="N53" s="9">
+      <c r="N53" s="14">
         <v>97900</v>
       </c>
-      <c r="O53" s="9">
+      <c r="O53" s="14">
         <v>98409</v>
       </c>
-      <c r="P53" s="9">
+      <c r="P53" s="14">
         <v>98509</v>
       </c>
-      <c r="Q53" s="9">
+      <c r="Q53" s="14">
         <v>98460</v>
       </c>
-      <c r="R53" s="9">
+      <c r="R53" s="14">
         <v>98704</v>
       </c>
-      <c r="S53" s="9">
+      <c r="S53" s="14">
         <v>98971</v>
       </c>
-      <c r="T53" s="9">
+      <c r="T53" s="14">
         <v>98971</v>
       </c>
-      <c r="U53" s="9">
+      <c r="U53" s="14">
         <v>100089</v>
       </c>
-      <c r="V53" s="9">
+      <c r="V53" s="14">
         <v>100461</v>
       </c>
-      <c r="W53" s="9">
+      <c r="W53" s="14">
         <v>100411</v>
       </c>
-      <c r="X53" s="9">
+      <c r="X53" s="27">
         <v>100261</v>
       </c>
-      <c r="Y53" s="10">
+      <c r="Y53" s="28">
         <v>-1.1349741647931211</v>
       </c>
-      <c r="Z53" s="10">
-        <v>1.2866418647330466</v>
-      </c>
-      <c r="AA53" s="10">
-        <v>-0.14960951915500545</v>
-      </c>
-    </row>
-    <row r="54" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="3">
+      <c r="Z53" s="28">
+        <v>1.3034121106182681</v>
+      </c>
+      <c r="AA53" s="28">
+        <v>-0.14938602344363971</v>
+      </c>
+    </row>
+    <row r="54" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="12">
         <v>456</v>
       </c>
-      <c r="C54" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="D54" s="9">
+      <c r="C54" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B54</f>
+        <v>Grafschaft Bentheim</v>
+      </c>
+      <c r="D54" s="14">
         <v>134442</v>
       </c>
-      <c r="E54" s="9">
+      <c r="E54" s="14">
         <v>134840</v>
       </c>
-      <c r="F54" s="9">
+      <c r="F54" s="14">
         <v>135270</v>
       </c>
-      <c r="G54" s="9">
+      <c r="G54" s="14">
         <v>135508</v>
       </c>
-      <c r="H54" s="9">
+      <c r="H54" s="14">
         <v>135346</v>
       </c>
-      <c r="I54" s="9">
+      <c r="I54" s="14">
         <v>135047</v>
       </c>
-      <c r="J54" s="9">
+      <c r="J54" s="14">
         <v>133400</v>
       </c>
-      <c r="K54" s="9">
+      <c r="K54" s="14">
         <v>133652</v>
       </c>
-      <c r="L54" s="9">
+      <c r="L54" s="14">
         <v>133678</v>
       </c>
-      <c r="M54" s="9">
+      <c r="M54" s="14">
         <v>134329</v>
       </c>
-      <c r="N54" s="9">
+      <c r="N54" s="14">
         <v>135662</v>
       </c>
-      <c r="O54" s="9">
+      <c r="O54" s="14">
         <v>135770</v>
       </c>
-      <c r="P54" s="9">
+      <c r="P54" s="14">
         <v>135859</v>
       </c>
-      <c r="Q54" s="9">
+      <c r="Q54" s="14">
         <v>136511</v>
       </c>
-      <c r="R54" s="9">
+      <c r="R54" s="14">
         <v>137162</v>
       </c>
-      <c r="S54" s="9">
+      <c r="S54" s="14">
         <v>137891</v>
       </c>
-      <c r="T54" s="9">
+      <c r="T54" s="14">
         <v>138722</v>
       </c>
-      <c r="U54" s="9">
+      <c r="U54" s="14">
         <v>143472</v>
       </c>
-      <c r="V54" s="9">
+      <c r="V54" s="14">
         <v>144212</v>
       </c>
-      <c r="W54" s="9">
+      <c r="W54" s="14">
         <v>144543</v>
       </c>
-      <c r="X54" s="9">
+      <c r="X54" s="27">
         <v>144674</v>
       </c>
-      <c r="Y54" s="10">
+      <c r="Y54" s="28">
         <v>7.6107168890674046</v>
       </c>
-      <c r="Z54" s="10">
-        <v>4.6884720129394362</v>
-      </c>
-      <c r="AA54" s="10">
-        <v>9.0548405380372426E-2</v>
-      </c>
-    </row>
-    <row r="55" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="3">
+      <c r="Z54" s="28">
+        <v>4.9191027695788705</v>
+      </c>
+      <c r="AA54" s="28">
+        <v>9.0630469825583759E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="12">
         <v>457</v>
       </c>
-      <c r="C55" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="D55" s="9">
+      <c r="C55" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B55</f>
+        <v>Leer</v>
+      </c>
+      <c r="D55" s="14">
         <v>165056</v>
       </c>
-      <c r="E55" s="9">
+      <c r="E55" s="14">
         <v>165347</v>
       </c>
-      <c r="F55" s="9">
+      <c r="F55" s="14">
         <v>165088</v>
       </c>
-      <c r="G55" s="9">
+      <c r="G55" s="14">
         <v>164947</v>
       </c>
-      <c r="H55" s="9">
+      <c r="H55" s="14">
         <v>164837</v>
       </c>
-      <c r="I55" s="9">
+      <c r="I55" s="14">
         <v>164705</v>
       </c>
-      <c r="J55" s="9">
+      <c r="J55" s="14">
         <v>163991</v>
       </c>
-      <c r="K55" s="9">
+      <c r="K55" s="14">
         <v>164202</v>
       </c>
-      <c r="L55" s="9">
+      <c r="L55" s="14">
         <v>164792</v>
       </c>
-      <c r="M55" s="9">
+      <c r="M55" s="14">
         <v>165809</v>
       </c>
-      <c r="N55" s="9">
+      <c r="N55" s="14">
         <v>167548</v>
       </c>
-      <c r="O55" s="9">
+      <c r="O55" s="14">
         <v>168253</v>
       </c>
-      <c r="P55" s="9">
+      <c r="P55" s="14">
         <v>168946</v>
       </c>
-      <c r="Q55" s="9">
+      <c r="Q55" s="14">
         <v>169809</v>
       </c>
-      <c r="R55" s="9">
+      <c r="R55" s="14">
         <v>170756</v>
       </c>
-      <c r="S55" s="9">
+      <c r="S55" s="14">
         <v>171483</v>
       </c>
-      <c r="T55" s="9">
+      <c r="T55" s="14">
         <v>172421</v>
       </c>
-      <c r="U55" s="9">
+      <c r="U55" s="14">
         <v>169390</v>
       </c>
-      <c r="V55" s="9">
+      <c r="V55" s="14">
         <v>169111</v>
       </c>
-      <c r="W55" s="9">
+      <c r="W55" s="14">
         <v>169103</v>
       </c>
-      <c r="X55" s="9">
+      <c r="X55" s="27">
         <v>169111</v>
       </c>
-      <c r="Y55" s="10">
-        <v>2.4567419542458317</v>
-      </c>
-      <c r="Z55" s="10">
-        <v>-1.4026290424632342</v>
-      </c>
-      <c r="AA55" s="10">
-        <v>4.7306207165707728E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="3">
+      <c r="Y55" s="28">
+        <v>2.4567419542458282</v>
+      </c>
+      <c r="Z55" s="28">
+        <v>-1.3832274919379728</v>
+      </c>
+      <c r="AA55" s="28">
+        <v>4.7308445148814826E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="12">
         <v>458</v>
       </c>
-      <c r="C56" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D56" s="9">
+      <c r="C56" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B56</f>
+        <v>Oldenburg</v>
+      </c>
+      <c r="D56" s="14">
         <v>125731</v>
       </c>
-      <c r="E56" s="9">
+      <c r="E56" s="14">
         <v>125949</v>
       </c>
-      <c r="F56" s="9">
+      <c r="F56" s="14">
         <v>126131</v>
       </c>
-      <c r="G56" s="9">
+      <c r="G56" s="14">
         <v>125943</v>
       </c>
-      <c r="H56" s="9">
+      <c r="H56" s="14">
         <v>126571</v>
       </c>
-      <c r="I56" s="9">
+      <c r="I56" s="14">
         <v>127282</v>
       </c>
-      <c r="J56" s="9">
+      <c r="J56" s="14">
         <v>125265</v>
       </c>
-      <c r="K56" s="9">
+      <c r="K56" s="14">
         <v>125413</v>
       </c>
-      <c r="L56" s="9">
+      <c r="L56" s="14">
         <v>125778</v>
       </c>
-      <c r="M56" s="9">
+      <c r="M56" s="14">
         <v>126798</v>
       </c>
-      <c r="N56" s="9">
+      <c r="N56" s="14">
         <v>128608</v>
       </c>
-      <c r="O56" s="9">
+      <c r="O56" s="14">
         <v>129484</v>
       </c>
-      <c r="P56" s="9">
+      <c r="P56" s="14">
         <v>129924</v>
       </c>
-      <c r="Q56" s="9">
+      <c r="Q56" s="14">
         <v>130144</v>
       </c>
-      <c r="R56" s="9">
+      <c r="R56" s="14">
         <v>130890</v>
       </c>
-      <c r="S56" s="9">
+      <c r="S56" s="14">
         <v>131467</v>
       </c>
-      <c r="T56" s="9">
+      <c r="T56" s="14">
         <v>132091</v>
       </c>
-      <c r="U56" s="9">
+      <c r="U56" s="14">
         <v>131228</v>
       </c>
-      <c r="V56" s="9">
+      <c r="V56" s="14">
         <v>131965</v>
       </c>
-      <c r="W56" s="9">
+      <c r="W56" s="14">
         <v>132008</v>
       </c>
-      <c r="X56" s="9">
+      <c r="X56" s="27">
         <v>132176</v>
       </c>
-      <c r="Y56" s="10">
-        <v>5.126023017394278</v>
-      </c>
-      <c r="Z56" s="10">
-        <v>0.53640600411572448</v>
-      </c>
-      <c r="AA56" s="10">
-        <v>0.12710325626437477</v>
-      </c>
-    </row>
-    <row r="57" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="3">
+      <c r="Y56" s="28">
+        <v>5.1260230173942745</v>
+      </c>
+      <c r="Z56" s="28">
+        <v>0.53929883544920187</v>
+      </c>
+      <c r="AA56" s="28">
+        <v>0.12726501424155856</v>
+      </c>
+    </row>
+    <row r="57" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="12">
         <v>459</v>
       </c>
-      <c r="C57" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D57" s="9">
+      <c r="C57" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B57</f>
+        <v>Osnabrück</v>
+      </c>
+      <c r="D57" s="14">
         <v>359449</v>
       </c>
-      <c r="E57" s="9">
+      <c r="E57" s="14">
         <v>359340</v>
       </c>
-      <c r="F57" s="9">
+      <c r="F57" s="14">
         <v>358852</v>
       </c>
-      <c r="G57" s="9">
+      <c r="G57" s="14">
         <v>358236</v>
       </c>
-      <c r="H57" s="9">
+      <c r="H57" s="14">
         <v>357056</v>
       </c>
-      <c r="I57" s="9">
+      <c r="I57" s="14">
         <v>356123</v>
       </c>
-      <c r="J57" s="9">
+      <c r="J57" s="14">
         <v>350418</v>
       </c>
-      <c r="K57" s="9">
+      <c r="K57" s="14">
         <v>350444</v>
       </c>
-      <c r="L57" s="9">
+      <c r="L57" s="14">
         <v>350302</v>
       </c>
-      <c r="M57" s="9">
+      <c r="M57" s="14">
         <v>351316</v>
       </c>
-      <c r="N57" s="9">
+      <c r="N57" s="14">
         <v>358079</v>
       </c>
-      <c r="O57" s="9">
+      <c r="O57" s="14">
         <v>354807</v>
       </c>
-      <c r="P57" s="9">
+      <c r="P57" s="14">
         <v>356140</v>
       </c>
-      <c r="Q57" s="9">
+      <c r="Q57" s="14">
         <v>357343</v>
       </c>
-      <c r="R57" s="9">
+      <c r="R57" s="14">
         <v>358080</v>
       </c>
-      <c r="S57" s="9">
+      <c r="S57" s="14">
         <v>359471</v>
       </c>
-      <c r="T57" s="9">
+      <c r="T57" s="14">
         <v>361550</v>
       </c>
-      <c r="U57" s="9">
+      <c r="U57" s="14">
         <v>356060</v>
       </c>
-      <c r="V57" s="9">
+      <c r="V57" s="14">
         <v>356194</v>
       </c>
-      <c r="W57" s="9">
+      <c r="W57" s="14">
         <v>354821</v>
       </c>
-      <c r="X57" s="9">
+      <c r="X57" s="27">
         <v>354130</v>
       </c>
-      <c r="Y57" s="10">
-        <v>-1.4797648623309565</v>
-      </c>
-      <c r="Z57" s="10">
-        <v>-1.5082032022138763</v>
-      </c>
-      <c r="AA57" s="10">
-        <v>-0.19512608364160053</v>
-      </c>
-    </row>
-    <row r="58" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="3">
+      <c r="Y57" s="28">
+        <v>-1.4797648623309527</v>
+      </c>
+      <c r="Z57" s="28">
+        <v>-1.4857944034428385</v>
+      </c>
+      <c r="AA57" s="28">
+        <v>-0.19474608323633902</v>
+      </c>
+    </row>
+    <row r="58" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="12">
         <v>460</v>
       </c>
-      <c r="C58" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="D58" s="9">
+      <c r="C58" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B58</f>
+        <v>Vechta</v>
+      </c>
+      <c r="D58" s="14">
         <v>132401</v>
       </c>
-      <c r="E58" s="9">
+      <c r="E58" s="14">
         <v>133104</v>
       </c>
-      <c r="F58" s="9">
+      <c r="F58" s="14">
         <v>134404</v>
       </c>
-      <c r="G58" s="9">
+      <c r="G58" s="14">
         <v>134506</v>
       </c>
-      <c r="H58" s="9">
+      <c r="H58" s="14">
         <v>134838</v>
       </c>
-      <c r="I58" s="9">
+      <c r="I58" s="14">
         <v>135374</v>
       </c>
-      <c r="J58" s="9">
+      <c r="J58" s="14">
         <v>132752</v>
       </c>
-      <c r="K58" s="9">
+      <c r="K58" s="14">
         <v>133462</v>
       </c>
-      <c r="L58" s="9">
+      <c r="L58" s="14">
         <v>134188</v>
       </c>
-      <c r="M58" s="9">
+      <c r="M58" s="14">
         <v>136184</v>
       </c>
-      <c r="N58" s="9">
+      <c r="N58" s="14">
         <v>137866</v>
       </c>
-      <c r="O58" s="9">
+      <c r="O58" s="14">
         <v>139671</v>
       </c>
-      <c r="P58" s="9">
+      <c r="P58" s="14">
         <v>140540</v>
       </c>
-      <c r="Q58" s="9">
+      <c r="Q58" s="14">
         <v>141598</v>
       </c>
-      <c r="R58" s="9">
+      <c r="R58" s="14">
         <v>142814</v>
       </c>
-      <c r="S58" s="9">
+      <c r="S58" s="14">
         <v>143698</v>
       </c>
-      <c r="T58" s="9">
+      <c r="T58" s="14">
         <v>144805</v>
       </c>
-      <c r="U58" s="9">
+      <c r="U58" s="14">
         <v>145552</v>
       </c>
-      <c r="V58" s="9">
+      <c r="V58" s="14">
         <v>146400</v>
       </c>
-      <c r="W58" s="9">
+      <c r="W58" s="14">
         <v>146539</v>
       </c>
-      <c r="X58" s="9">
+      <c r="X58" s="27">
         <v>146838</v>
       </c>
-      <c r="Y58" s="10">
-        <v>10.903996193382225</v>
-      </c>
-      <c r="Z58" s="10">
-        <v>2.138411038014683</v>
-      </c>
-      <c r="AA58" s="10">
-        <v>0.20362576444789496</v>
-      </c>
-    </row>
-    <row r="59" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="3">
+      <c r="Y58" s="28">
+        <v>10.903996193382227</v>
+      </c>
+      <c r="Z58" s="28">
+        <v>2.1851382761068407</v>
+      </c>
+      <c r="AA58" s="28">
+        <v>0.20404124499279419</v>
+      </c>
+    </row>
+    <row r="59" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="12">
         <v>461</v>
       </c>
-      <c r="C59" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="D59" s="9">
+      <c r="C59" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B59</f>
+        <v>Wesermarsch</v>
+      </c>
+      <c r="D59" s="14">
         <v>93725</v>
       </c>
-      <c r="E59" s="9">
+      <c r="E59" s="14">
         <v>93094</v>
       </c>
-      <c r="F59" s="9">
+      <c r="F59" s="14">
         <v>92622</v>
       </c>
-      <c r="G59" s="9">
+      <c r="G59" s="14">
         <v>91968</v>
       </c>
-      <c r="H59" s="9">
+      <c r="H59" s="14">
         <v>91228</v>
       </c>
-      <c r="I59" s="9">
+      <c r="I59" s="14">
         <v>90772</v>
       </c>
-      <c r="J59" s="9">
+      <c r="J59" s="14">
         <v>89527</v>
       </c>
-      <c r="K59" s="9">
+      <c r="K59" s="14">
         <v>89126</v>
       </c>
-      <c r="L59" s="9">
+      <c r="L59" s="14">
         <v>88831</v>
       </c>
-      <c r="M59" s="9">
+      <c r="M59" s="14">
         <v>88765</v>
       </c>
-      <c r="N59" s="9">
+      <c r="N59" s="14">
         <v>89239</v>
       </c>
-      <c r="O59" s="9">
+      <c r="O59" s="14">
         <v>89282</v>
       </c>
-      <c r="P59" s="9">
+      <c r="P59" s="14">
         <v>89022</v>
       </c>
-      <c r="Q59" s="9">
+      <c r="Q59" s="14">
         <v>88624</v>
       </c>
-      <c r="R59" s="9">
+      <c r="R59" s="14">
         <v>88583</v>
       </c>
-      <c r="S59" s="9">
+      <c r="S59" s="14">
         <v>88524</v>
       </c>
-      <c r="T59" s="9">
+      <c r="T59" s="14">
         <v>88430</v>
       </c>
-      <c r="U59" s="9">
+      <c r="U59" s="14">
         <v>89127</v>
       </c>
-      <c r="V59" s="9">
+      <c r="V59" s="14">
         <v>89316</v>
       </c>
-      <c r="W59" s="9">
+      <c r="W59" s="14">
         <v>88936</v>
       </c>
-      <c r="X59" s="9">
+      <c r="X59" s="27">
         <v>88852</v>
       </c>
-      <c r="Y59" s="10">
+      <c r="Y59" s="28">
         <v>-5.1992531341691119</v>
       </c>
-      <c r="Z59" s="10">
-        <v>0.36915319857740964</v>
-      </c>
-      <c r="AA59" s="10">
-        <v>-9.4539233782019533E-2</v>
-      </c>
-    </row>
-    <row r="60" spans="2:27" s="3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="3">
+      <c r="Z59" s="28">
+        <v>0.3705209886584413</v>
+      </c>
+      <c r="AA59" s="28">
+        <v>-9.4449941530982073E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="2:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="12">
         <v>462</v>
       </c>
-      <c r="C60" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="D60" s="9">
+      <c r="C60" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B60</f>
+        <v>Wittmund</v>
+      </c>
+      <c r="D60" s="14">
         <v>57954</v>
       </c>
-      <c r="E60" s="9">
+      <c r="E60" s="14">
         <v>57829</v>
       </c>
-      <c r="F60" s="9">
+      <c r="F60" s="14">
         <v>57742</v>
       </c>
-      <c r="G60" s="9">
+      <c r="G60" s="14">
         <v>57492</v>
       </c>
-      <c r="H60" s="9">
+      <c r="H60" s="14">
         <v>57391</v>
       </c>
-      <c r="I60" s="9">
+      <c r="I60" s="14">
         <v>57280</v>
       </c>
-      <c r="J60" s="9">
+      <c r="J60" s="14">
         <v>56572</v>
       </c>
-      <c r="K60" s="9">
+      <c r="K60" s="14">
         <v>56362</v>
       </c>
-      <c r="L60" s="9">
+      <c r="L60" s="14">
         <v>56400</v>
       </c>
-      <c r="M60" s="9">
+      <c r="M60" s="14">
         <v>56539</v>
       </c>
-      <c r="N60" s="9">
+      <c r="N60" s="14">
         <v>57173</v>
       </c>
-      <c r="O60" s="9">
+      <c r="O60" s="14">
         <v>56881</v>
       </c>
-      <c r="P60" s="9">
+      <c r="P60" s="14">
         <v>56731</v>
       </c>
-      <c r="Q60" s="9">
+      <c r="Q60" s="14">
         <v>56882</v>
       </c>
-      <c r="R60" s="9">
+      <c r="R60" s="14">
         <v>56926</v>
       </c>
-      <c r="S60" s="9">
+      <c r="S60" s="14">
         <v>57384</v>
       </c>
-      <c r="T60" s="9">
+      <c r="T60" s="14">
         <v>57455</v>
       </c>
-      <c r="U60" s="9">
+      <c r="U60" s="14">
         <v>55953</v>
       </c>
-      <c r="V60" s="9">
+      <c r="V60" s="14">
         <v>56013</v>
       </c>
-      <c r="W60" s="9">
+      <c r="W60" s="14">
         <v>55969</v>
       </c>
-      <c r="X60" s="9">
+      <c r="X60" s="27">
         <v>55849</v>
       </c>
-      <c r="Y60" s="10">
-        <v>-3.6321910480726092</v>
-      </c>
-      <c r="Z60" s="10">
-        <v>-2.7484825153539005</v>
-      </c>
-      <c r="AA60" s="10">
-        <v>-0.21486508263352969</v>
-      </c>
-    </row>
-    <row r="61" spans="2:27" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="5">
+      <c r="Y60" s="28">
+        <v>-3.6321910480726132</v>
+      </c>
+      <c r="Z60" s="28">
+        <v>-2.6749616617872647</v>
+      </c>
+      <c r="AA60" s="28">
+        <v>-0.2144044024370686</v>
+      </c>
+    </row>
+    <row r="61" spans="2:27" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="15">
         <v>4</v>
       </c>
-      <c r="C61" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="D61" s="11">
+      <c r="C61" s="16" t="str">
+        <f>[1]A1_2021_Berechnung!B61</f>
+        <v>Statistische Region Weser-Ems</v>
+      </c>
+      <c r="D61" s="17">
         <v>2475459</v>
       </c>
-      <c r="E61" s="11">
+      <c r="E61" s="17">
         <v>2477718</v>
       </c>
-      <c r="F61" s="11">
+      <c r="F61" s="17">
         <v>2480393</v>
       </c>
-      <c r="G61" s="11">
+      <c r="G61" s="17">
         <v>2477771</v>
       </c>
-      <c r="H61" s="11">
+      <c r="H61" s="17">
         <v>2476001</v>
       </c>
-      <c r="I61" s="11">
+      <c r="I61" s="17">
         <v>2477975</v>
       </c>
-      <c r="J61" s="11">
+      <c r="J61" s="17">
         <v>2437727</v>
       </c>
-      <c r="K61" s="11">
+      <c r="K61" s="17">
         <v>2442205</v>
       </c>
-      <c r="L61" s="11">
+      <c r="L61" s="17">
         <v>2446345</v>
       </c>
-      <c r="M61" s="11">
+      <c r="M61" s="17">
         <v>2460857</v>
       </c>
-      <c r="N61" s="11">
+      <c r="N61" s="17">
         <v>2496176</v>
       </c>
-      <c r="O61" s="11">
+      <c r="O61" s="17">
         <v>2506155</v>
       </c>
-      <c r="P61" s="11">
+      <c r="P61" s="17">
         <v>2516457</v>
       </c>
-      <c r="Q61" s="11">
+      <c r="Q61" s="17">
         <v>2525333</v>
       </c>
-      <c r="R61" s="11">
+      <c r="R61" s="17">
         <v>2533993</v>
       </c>
-      <c r="S61" s="11">
+      <c r="S61" s="17">
         <v>2542666</v>
       </c>
-      <c r="T61" s="11">
+      <c r="T61" s="17">
         <v>2554217</v>
       </c>
-      <c r="U61" s="11">
+      <c r="U61" s="17">
         <v>2559680</v>
       </c>
-      <c r="V61" s="11">
+      <c r="V61" s="17">
         <v>2570052</v>
       </c>
-      <c r="W61" s="11">
+      <c r="W61" s="17">
         <v>2569485</v>
       </c>
-      <c r="X61" s="11">
+      <c r="X61" s="29">
         <v>2569144</v>
       </c>
-      <c r="Y61" s="10">
-        <v>3.7845506631295449</v>
-      </c>
-      <c r="Z61" s="10">
-        <v>1.0306156447439303</v>
-      </c>
-      <c r="AA61" s="10">
-        <v>-1.3272903348352603E-2</v>
-      </c>
-    </row>
-    <row r="62" spans="2:27" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="5">
+      <c r="Y61" s="28">
+        <v>3.7845506631295507</v>
+      </c>
+      <c r="Z61" s="28">
+        <v>1.041347939524897</v>
+      </c>
+      <c r="AA61" s="28">
+        <v>-1.3271141882512438E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="2:27" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="15">
         <v>0</v>
       </c>
-      <c r="C62" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="D62" s="11">
+      <c r="C62" s="16" t="str">
+        <f>[1]A1_2021_Berechnung!B62</f>
+        <v>Niedersachsen</v>
+      </c>
+      <c r="D62" s="17">
         <v>7993946</v>
       </c>
-      <c r="E62" s="11">
+      <c r="E62" s="17">
         <v>7982685</v>
       </c>
-      <c r="F62" s="11">
+      <c r="F62" s="17">
         <v>7971684</v>
       </c>
-      <c r="G62" s="11">
+      <c r="G62" s="17">
         <v>7947244</v>
       </c>
-      <c r="H62" s="11">
+      <c r="H62" s="17">
         <v>7928815</v>
       </c>
-      <c r="I62" s="11">
+      <c r="I62" s="17">
         <v>7918293</v>
       </c>
-      <c r="J62" s="11">
+      <c r="J62" s="17">
         <v>7774253</v>
       </c>
-      <c r="K62" s="11">
+      <c r="K62" s="17">
         <v>7778995</v>
       </c>
-      <c r="L62" s="11">
+      <c r="L62" s="17">
         <v>7790559</v>
       </c>
-      <c r="M62" s="11">
+      <c r="M62" s="17">
         <v>7826739</v>
       </c>
-      <c r="N62" s="11">
+      <c r="N62" s="17">
         <v>7926599</v>
       </c>
-      <c r="O62" s="11">
+      <c r="O62" s="17">
         <v>7945685</v>
       </c>
-      <c r="P62" s="11">
+      <c r="P62" s="17">
         <v>7962775</v>
       </c>
-      <c r="Q62" s="11">
+      <c r="Q62" s="17">
         <v>7982448</v>
       </c>
-      <c r="R62" s="11">
+      <c r="R62" s="17">
         <v>7993608</v>
       </c>
-      <c r="S62" s="11">
+      <c r="S62" s="17">
         <v>8003421</v>
       </c>
-      <c r="T62" s="11">
+      <c r="T62" s="17">
         <v>8027031</v>
       </c>
-      <c r="U62" s="11">
+      <c r="U62" s="17">
         <v>7982947</v>
       </c>
-      <c r="V62" s="11">
+      <c r="V62" s="17">
         <v>8008135</v>
       </c>
-      <c r="W62" s="11">
+      <c r="W62" s="17">
         <v>8004489</v>
       </c>
-      <c r="X62" s="11">
+      <c r="X62" s="29">
         <v>8000826</v>
       </c>
-      <c r="Y62" s="10">
-        <v>8.6065129786966288E-2</v>
-      </c>
-      <c r="Z62" s="10">
-        <v>-3.2434151173891299E-2</v>
-      </c>
-      <c r="AA62" s="10">
-        <v>-4.5782772928695113E-2</v>
-      </c>
-    </row>
-    <row r="63" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="C63" s="12"/>
-    </row>
-    <row r="64" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="C64" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="65" spans="3:27" x14ac:dyDescent="0.25">
-      <c r="C65" s="3"/>
-    </row>
-    <row r="66" spans="3:27" x14ac:dyDescent="0.25">
-      <c r="C66" s="3"/>
-    </row>
-    <row r="67" spans="3:27" x14ac:dyDescent="0.25">
-      <c r="C67" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="69" spans="3:27" x14ac:dyDescent="0.25">
-      <c r="C69" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="7"/>
-      <c r="G69" s="7"/>
-      <c r="H69" s="7"/>
-      <c r="I69" s="7"/>
-      <c r="J69" s="7"/>
-      <c r="K69" s="7"/>
-      <c r="L69" s="3"/>
-      <c r="M69" s="3"/>
-      <c r="N69" s="3"/>
-      <c r="O69" s="3"/>
-      <c r="P69" s="3"/>
-      <c r="Q69" s="3"/>
-      <c r="R69" s="3"/>
-      <c r="S69" s="3"/>
-      <c r="T69" s="3"/>
-      <c r="U69" s="3"/>
-      <c r="V69" s="3"/>
-      <c r="W69" s="3"/>
-      <c r="X69" s="3"/>
-      <c r="Y69" s="3"/>
-      <c r="Z69" s="3"/>
-      <c r="AA69" s="3"/>
-    </row>
-    <row r="70" spans="3:27" x14ac:dyDescent="0.25">
-      <c r="C70" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="7"/>
-      <c r="G70" s="7"/>
-      <c r="H70" s="7"/>
-      <c r="I70" s="7"/>
-      <c r="J70" s="7"/>
-      <c r="K70" s="7"/>
-      <c r="L70" s="3"/>
-      <c r="M70" s="3"/>
-      <c r="N70" s="3"/>
-      <c r="O70" s="3"/>
-      <c r="P70" s="3"/>
-      <c r="Q70" s="3"/>
-      <c r="R70" s="3"/>
-      <c r="S70" s="3"/>
-      <c r="T70" s="3"/>
-      <c r="U70" s="3"/>
-      <c r="V70" s="3"/>
-      <c r="W70" s="3"/>
-      <c r="X70" s="3"/>
-      <c r="Y70" s="3"/>
-      <c r="Z70" s="3"/>
-      <c r="AA70" s="3"/>
-    </row>
-    <row r="71" spans="3:27" x14ac:dyDescent="0.25">
-      <c r="C71" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="7"/>
-      <c r="G71" s="7"/>
-      <c r="H71" s="7"/>
-      <c r="I71" s="7"/>
-      <c r="J71" s="7"/>
-      <c r="K71" s="7"/>
-      <c r="L71" s="3"/>
-      <c r="M71" s="3"/>
-      <c r="N71" s="3"/>
-      <c r="O71" s="3"/>
-      <c r="P71" s="3"/>
-      <c r="Q71" s="3"/>
-      <c r="R71" s="3"/>
-      <c r="S71" s="3"/>
-      <c r="T71" s="3"/>
-      <c r="U71" s="3"/>
-      <c r="V71" s="3"/>
-      <c r="W71" s="3"/>
-      <c r="X71" s="3"/>
-      <c r="Y71" s="3"/>
-      <c r="Z71" s="3"/>
-      <c r="AA71" s="3"/>
-    </row>
-    <row r="72" spans="3:27" x14ac:dyDescent="0.25">
-      <c r="C72" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7"/>
-      <c r="G72" s="7"/>
-      <c r="H72" s="7"/>
-      <c r="I72" s="7"/>
-      <c r="J72" s="7"/>
-      <c r="K72" s="7"/>
-      <c r="L72" s="3"/>
-      <c r="M72" s="3"/>
-      <c r="N72" s="3"/>
-      <c r="O72" s="3"/>
-      <c r="P72" s="3"/>
-      <c r="Q72" s="3"/>
-      <c r="R72" s="3"/>
-      <c r="S72" s="3"/>
-      <c r="T72" s="3"/>
-      <c r="U72" s="3"/>
-      <c r="V72" s="3"/>
-      <c r="W72" s="3"/>
-      <c r="X72" s="3"/>
-      <c r="Y72" s="3"/>
-      <c r="Z72" s="3"/>
-      <c r="AA72" s="3"/>
+      <c r="Y62" s="28">
+        <v>8.606512978695946E-2</v>
+      </c>
+      <c r="Z62" s="28">
+        <v>-3.2423634843155469E-2</v>
+      </c>
+      <c r="AA62" s="28">
+        <v>-4.576182189768474E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="2:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C64" s="13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="3:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C65" s="12"/>
+    </row>
+    <row r="66" spans="3:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C66" s="12"/>
+    </row>
+    <row r="67" spans="3:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C67" s="13" t="str">
+        <f>[1]A1_2021_Berechnung!B67</f>
+        <v>Quelle: Bevölkerungsfortschreibung</v>
+      </c>
+    </row>
+    <row r="68" spans="3:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="3:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C69" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="19"/>
+      <c r="K69" s="19"/>
+      <c r="X69" s="30"/>
+      <c r="Y69" s="30"/>
+      <c r="Z69" s="30"/>
+      <c r="AA69" s="30"/>
+    </row>
+    <row r="70" spans="3:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C70" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D70" s="19"/>
+      <c r="E70" s="19"/>
+      <c r="F70" s="19"/>
+      <c r="G70" s="19"/>
+      <c r="H70" s="19"/>
+      <c r="I70" s="19"/>
+      <c r="J70" s="19"/>
+      <c r="K70" s="19"/>
+      <c r="X70" s="30"/>
+      <c r="Y70" s="30"/>
+      <c r="Z70" s="30"/>
+      <c r="AA70" s="30"/>
+    </row>
+    <row r="71" spans="3:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C71" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D71" s="19"/>
+      <c r="E71" s="19"/>
+      <c r="F71" s="19"/>
+      <c r="G71" s="19"/>
+      <c r="H71" s="19"/>
+      <c r="I71" s="19"/>
+      <c r="J71" s="19"/>
+      <c r="K71" s="19"/>
+      <c r="X71" s="30"/>
+      <c r="Y71" s="30"/>
+      <c r="Z71" s="30"/>
+      <c r="AA71" s="30"/>
+    </row>
+    <row r="72" spans="3:27" s="12" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C72" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="D72" s="19"/>
+      <c r="E72" s="19"/>
+      <c r="F72" s="19"/>
+      <c r="G72" s="19"/>
+      <c r="H72" s="19"/>
+      <c r="I72" s="19"/>
+      <c r="J72" s="19"/>
+      <c r="K72" s="19"/>
+      <c r="X72" s="30"/>
+      <c r="Y72" s="30"/>
+      <c r="Z72" s="30"/>
+      <c r="AA72" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -5389,7 +5642,7 @@
     <mergeCell ref="Y9:AA9"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C72" r:id="rId1" xr:uid="{F87C8E0E-A8CB-4FAF-AF1F-2F071C91DBD4}"/>
+    <hyperlink ref="C72" r:id="rId1" xr:uid="{C308EE96-AD3B-4061-A7F0-860C647CD0A5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
